--- a/data/omxs30_modell_gissningar.xlsx
+++ b/data/omxs30_modell_gissningar.xlsx
@@ -455,7 +455,7 @@
         <v>-0.04906913963285997</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001476627730980677</v>
+        <v>-0.004835902837895359</v>
       </c>
     </row>
     <row r="3">
@@ -471,7 +471,7 @@
         <v>0.02655147948824843</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002497540961053359</v>
+        <v>0.002681433787198829</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.01823363896450658</v>
+        <v>0.01823372501456944</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002430977986984346</v>
+        <v>0.006018767125926201</v>
       </c>
     </row>
     <row r="5">
@@ -500,10 +500,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0880614755781548</v>
+        <v>0.08806138678909092</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00465763389226501</v>
+        <v>-0.007776958782052455</v>
       </c>
     </row>
     <row r="6">
@@ -519,7 +519,7 @@
         <v>0.03446220003181466</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001588380660598743</v>
+        <v>-0.006996438233772693</v>
       </c>
     </row>
     <row r="7">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01869562080480125</v>
+        <v>0.01869554851138888</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.000274526500922437</v>
+        <v>-0.01072696757072836</v>
       </c>
     </row>
     <row r="8">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01847998849650256</v>
+        <v>0.01848013328384801</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003013026700663717</v>
+        <v>-0.006082998041198814</v>
       </c>
     </row>
     <row r="9">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.04806151202482978</v>
+        <v>-0.04806158109733583</v>
       </c>
       <c r="D9" t="n">
-        <v>0.006618126340864425</v>
+        <v>-0.003691174407301356</v>
       </c>
     </row>
     <row r="10">
@@ -580,10 +580,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.006502860447886949</v>
+        <v>-0.006502938861282836</v>
       </c>
       <c r="D10" t="n">
-        <v>0.008452337331393207</v>
+        <v>-0.001639973137651306</v>
       </c>
     </row>
     <row r="11">
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.03976579389371726</v>
+        <v>0.03976580334087254</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01221943437887312</v>
+        <v>-0.002331115714472937</v>
       </c>
     </row>
     <row r="12">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.006617912112146795</v>
+        <v>-0.006617833635704784</v>
       </c>
       <c r="D12" t="n">
-        <v>0.006473611177585704</v>
+        <v>-0.001617976471904709</v>
       </c>
     </row>
     <row r="13">
@@ -631,7 +631,7 @@
         <v>0.009474080447880451</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.002080859899441132</v>
+        <v>-0.004996493934583502</v>
       </c>
     </row>
     <row r="14">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.04246999557100306</v>
+        <v>0.04246992617390299</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.002279531757245826</v>
+        <v>-0.001258832555698843</v>
       </c>
     </row>
     <row r="15">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.00853144119947391</v>
+        <v>0.00853150751674181</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.004151283098000104</v>
+        <v>-0.01152929695036845</v>
       </c>
     </row>
     <row r="16">
@@ -679,7 +679,7 @@
         <v>0.0851417710955078</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0009837522831094405</v>
+        <v>-0.007328715917929959</v>
       </c>
     </row>
     <row r="17">
@@ -695,7 +695,7 @@
         <v>0.0390402371053602</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.002041950990316363</v>
+        <v>-0.003962826075787374</v>
       </c>
     </row>
     <row r="18">
@@ -711,7 +711,7 @@
         <v>0.03484881716886523</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0001331951635629401</v>
+        <v>-0.01001746646813483</v>
       </c>
     </row>
     <row r="19">
@@ -727,7 +727,7 @@
         <v>-0.003956349349212074</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0005429234086118968</v>
+        <v>-0.008025648694424832</v>
       </c>
     </row>
     <row r="20">
@@ -743,7 +743,7 @@
         <v>-0.007653341888235299</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0004243589871786579</v>
+        <v>-0.01133413374913633</v>
       </c>
     </row>
     <row r="21">
@@ -759,7 +759,7 @@
         <v>-0.01480677587825086</v>
       </c>
       <c r="D21" t="n">
-        <v>0.002121939422545986</v>
+        <v>-0.007731288703448002</v>
       </c>
     </row>
     <row r="22">
@@ -775,7 +775,7 @@
         <v>0.04497647131644433</v>
       </c>
       <c r="D22" t="n">
-        <v>0.006384808456603328</v>
+        <v>-0.002945065449099711</v>
       </c>
     </row>
     <row r="23">
@@ -791,7 +791,7 @@
         <v>0.05608994095857167</v>
       </c>
       <c r="D23" t="n">
-        <v>0.004320967289297842</v>
+        <v>-0.01060451951375009</v>
       </c>
     </row>
     <row r="24">
@@ -807,7 +807,7 @@
         <v>-0.02683302548336053</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00698652326420722</v>
+        <v>-0.01037096777577099</v>
       </c>
     </row>
     <row r="25">
@@ -823,7 +823,7 @@
         <v>-0.05565913051131877</v>
       </c>
       <c r="D25" t="n">
-        <v>0.005525553499266768</v>
+        <v>-0.008212435165082065</v>
       </c>
     </row>
     <row r="26">
@@ -839,7 +839,7 @@
         <v>-0.07429886483876913</v>
       </c>
       <c r="D26" t="n">
-        <v>0.004221188131788631</v>
+        <v>-0.007333819818817346</v>
       </c>
     </row>
     <row r="27">
@@ -855,7 +855,7 @@
         <v>-0.01864926668791356</v>
       </c>
       <c r="D27" t="n">
-        <v>0.008177254054947096</v>
+        <v>-0.0008841925337888272</v>
       </c>
     </row>
     <row r="28">
@@ -871,7 +871,7 @@
         <v>0.01122165816978915</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01693105396959857</v>
+        <v>0.009683397951962453</v>
       </c>
     </row>
     <row r="29">
@@ -887,7 +887,7 @@
         <v>0.04191222102538394</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01346057733108491</v>
+        <v>-0.005987374461043688</v>
       </c>
     </row>
     <row r="30">
@@ -903,7 +903,7 @@
         <v>0.0456836018839144</v>
       </c>
       <c r="D30" t="n">
-        <v>0.01057573769926665</v>
+        <v>-0.007834391349404536</v>
       </c>
     </row>
     <row r="31">
@@ -919,7 +919,7 @@
         <v>0.1013320644969831</v>
       </c>
       <c r="D31" t="n">
-        <v>0.009130271887895891</v>
+        <v>-0.004506389476488204</v>
       </c>
     </row>
     <row r="32">
@@ -935,7 +935,7 @@
         <v>-0.0279577792630481</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.006937741753527199</v>
+        <v>-0.0180289496293428</v>
       </c>
     </row>
     <row r="33">
@@ -951,7 +951,7 @@
         <v>0.0499810088439161</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.001969895647820899</v>
+        <v>-0.01188897125071995</v>
       </c>
     </row>
     <row r="34">
@@ -967,7 +967,7 @@
         <v>0.002484029278033706</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.00056542667693629</v>
+        <v>-0.007155183132105464</v>
       </c>
     </row>
     <row r="35">
@@ -983,7 +983,7 @@
         <v>-0.04150399672385319</v>
       </c>
       <c r="D35" t="n">
-        <v>0.004152333897809871</v>
+        <v>-0.009013801448703212</v>
       </c>
     </row>
     <row r="36">
@@ -999,7 +999,7 @@
         <v>-0.02475684765407404</v>
       </c>
       <c r="D36" t="n">
-        <v>0.007222929147829332</v>
+        <v>0.0003310146304849482</v>
       </c>
     </row>
     <row r="37">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.04221467271945212</v>
+        <v>0.04221466720882661</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0007939641873817055</v>
+        <v>-0.003335054083067198</v>
       </c>
     </row>
     <row r="38">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.07294152541477228</v>
+        <v>0.07294132884836757</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.001031657629364591</v>
+        <v>-0.009564977454903258</v>
       </c>
     </row>
     <row r="39">
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.01082426764399202</v>
+        <v>0.01082435901425693</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.001145152639824339</v>
+        <v>-0.003430986660083518</v>
       </c>
     </row>
     <row r="40">
@@ -1063,7 +1063,7 @@
         <v>0.05377014049998241</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.001134417447078666</v>
+        <v>-0.008056501820351036</v>
       </c>
     </row>
     <row r="41">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.02532141856482806</v>
+        <v>-0.02532150122794952</v>
       </c>
       <c r="D41" t="n">
-        <v>-4.966768963035606e-05</v>
+        <v>-0.007584509539953656</v>
       </c>
     </row>
     <row r="42">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.02782354720908331</v>
+        <v>0.02782371137692419</v>
       </c>
       <c r="D42" t="n">
-        <v>0.004237850081803886</v>
+        <v>-0.007354532537620846</v>
       </c>
     </row>
     <row r="43">
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.007314550628648164</v>
+        <v>0.007314470632700076</v>
       </c>
       <c r="D43" t="n">
-        <v>0.006790092534677077</v>
+        <v>-0.002577805611071108</v>
       </c>
     </row>
     <row r="44">
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.01101463787662205</v>
+        <v>-0.01101472152689231</v>
       </c>
       <c r="D44" t="n">
-        <v>0.009366927395748813</v>
+        <v>-0.002865366435534809</v>
       </c>
     </row>
     <row r="45">
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.003471705883841825</v>
+        <v>-0.00347153786657417</v>
       </c>
       <c r="D45" t="n">
-        <v>0.006895688771513723</v>
+        <v>-0.003374229798540173</v>
       </c>
     </row>
     <row r="46">
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.009938348436109301</v>
+        <v>0.009938162090141756</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01093387133376034</v>
+        <v>-0.005382507444064226</v>
       </c>
     </row>
     <row r="47">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.04356829352433822</v>
+        <v>-0.04356820867509792</v>
       </c>
       <c r="D47" t="n">
-        <v>0.006017831510729025</v>
+        <v>-0.002441912046773198</v>
       </c>
     </row>
     <row r="48">
@@ -1191,7 +1191,7 @@
         <v>-0.03050934713497022</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0007535580400037226</v>
+        <v>-0.002057696556886351</v>
       </c>
     </row>
     <row r="49">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.02624628235332316</v>
+        <v>-0.02624619846349274</v>
       </c>
       <c r="D49" t="n">
-        <v>0.002467477049846248</v>
+        <v>0.003578797757516528</v>
       </c>
     </row>
     <row r="50">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.05311727885186501</v>
+        <v>0.05311710688457971</v>
       </c>
       <c r="D50" t="n">
-        <v>0.002324870155394021</v>
+        <v>-0.005580763431120231</v>
       </c>
     </row>
     <row r="51">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.1286602440406261</v>
+        <v>0.1286603316254011</v>
       </c>
       <c r="D51" t="n">
-        <v>0.001866992558020059</v>
+        <v>-0.006784130512581595</v>
       </c>
     </row>
     <row r="52">
@@ -1255,7 +1255,7 @@
         <v>0.005834148771908687</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.002904016187317288</v>
+        <v>-0.006040752789728833</v>
       </c>
     </row>
     <row r="53">
@@ -1271,7 +1271,7 @@
         <v>-0.03018128505560147</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.002307787250115625</v>
+        <v>-0.008200142201092914</v>
       </c>
     </row>
     <row r="54">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.003655979715316171</v>
+        <v>0.003656048032092629</v>
       </c>
       <c r="D54" t="n">
-        <v>0.001890033086172813</v>
+        <v>-0.005269600249633719</v>
       </c>
     </row>
     <row r="55">
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-0.02257156860722742</v>
+        <v>-0.02257163378208071</v>
       </c>
       <c r="D55" t="n">
-        <v>0.003605120348253936</v>
+        <v>-0.009369038438051515</v>
       </c>
     </row>
     <row r="56">
@@ -1319,7 +1319,7 @@
         <v>0.04848918936355795</v>
       </c>
       <c r="D56" t="n">
-        <v>0.005338271323623337</v>
+        <v>-0.002555830335432563</v>
       </c>
     </row>
     <row r="57">
@@ -1335,7 +1335,7 @@
         <v>-0.004306343495218301</v>
       </c>
       <c r="D57" t="n">
-        <v>0.003895278473938256</v>
+        <v>-0.004164926475622568</v>
       </c>
     </row>
     <row r="58">
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.0006841502006704747</v>
+        <v>-0.0006840827271327177</v>
       </c>
       <c r="D58" t="n">
-        <v>0.004361210401242048</v>
+        <v>-0.0109599102587957</v>
       </c>
     </row>
     <row r="59">
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.00856290624272904</v>
+        <v>0.008562838205405265</v>
       </c>
       <c r="D59" t="n">
-        <v>0.008887836275947712</v>
+        <v>-0.006750133112573936</v>
       </c>
     </row>
     <row r="60">
@@ -1383,7 +1383,7 @@
         <v>-0.003925458608121213</v>
       </c>
       <c r="D60" t="n">
-        <v>0.008667407430990764</v>
+        <v>-0.0105372465462232</v>
       </c>
     </row>
     <row r="61">
@@ -1399,7 +1399,7 @@
         <v>-0.08322182904897146</v>
       </c>
       <c r="D61" t="n">
-        <v>0.002871467338623859</v>
+        <v>-0.006730561032463726</v>
       </c>
     </row>
     <row r="62">
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.008006221576132622</v>
+        <v>0.008006289834078584</v>
       </c>
       <c r="D62" t="n">
-        <v>0.004699891335683408</v>
+        <v>-4.973660866478945e-05</v>
       </c>
     </row>
     <row r="63">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-0.0226867072782625</v>
+        <v>-0.02268677774634964</v>
       </c>
       <c r="D63" t="n">
-        <v>0.01384232439542979</v>
+        <v>0.004606116052378093</v>
       </c>
     </row>
     <row r="64">
@@ -1447,7 +1447,7 @@
         <v>-0.006468352118571996</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0141798163654528</v>
+        <v>-0.007754742690104182</v>
       </c>
     </row>
     <row r="65">
@@ -1463,7 +1463,7 @@
         <v>-0.02326497719064902</v>
       </c>
       <c r="D65" t="n">
-        <v>0.01304941113097853</v>
+        <v>-0.003319187917335549</v>
       </c>
     </row>
     <row r="66">
@@ -1479,7 +1479,7 @@
         <v>0.03743658937241445</v>
       </c>
       <c r="D66" t="n">
-        <v>0.01585486342633988</v>
+        <v>0.0006473622203698017</v>
       </c>
     </row>
     <row r="67">
@@ -1495,7 +1495,7 @@
         <v>-0.008314780180495918</v>
       </c>
       <c r="D67" t="n">
-        <v>0.001120189997744613</v>
+        <v>-0.01096183652909832</v>
       </c>
     </row>
     <row r="68">
@@ -1511,7 +1511,7 @@
         <v>-0.01900767594342068</v>
       </c>
       <c r="D68" t="n">
-        <v>0.003063451031791684</v>
+        <v>-0.0110531809530331</v>
       </c>
     </row>
     <row r="69">
@@ -1527,7 +1527,7 @@
         <v>0.02059920939517079</v>
       </c>
       <c r="D69" t="n">
-        <v>0.004469703254219424</v>
+        <v>-0.004134056562980418</v>
       </c>
     </row>
     <row r="70">
@@ -1543,7 +1543,7 @@
         <v>-0.0257627121501498</v>
       </c>
       <c r="D70" t="n">
-        <v>0.005540960191445754</v>
+        <v>-0.008678212482760734</v>
       </c>
     </row>
     <row r="71">
@@ -1559,7 +1559,7 @@
         <v>0.01072410517255018</v>
       </c>
       <c r="D71" t="n">
-        <v>0.008785040412499147</v>
+        <v>-0.002398371722715618</v>
       </c>
     </row>
     <row r="72">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.02669604472690335</v>
+        <v>0.02669617737186236</v>
       </c>
       <c r="D72" t="n">
-        <v>0.004250295813301898</v>
+        <v>-0.001624727242754395</v>
       </c>
     </row>
     <row r="73">
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-0.02530889735724262</v>
+        <v>-0.02530895775649245</v>
       </c>
       <c r="D73" t="n">
-        <v>0.002401817871231223</v>
+        <v>-0.001890470989914635</v>
       </c>
     </row>
     <row r="74">
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-0.02882405430872481</v>
+        <v>-0.028824184895476</v>
       </c>
       <c r="D74" t="n">
-        <v>0.00342492447275858</v>
+        <v>0.006801532556165793</v>
       </c>
     </row>
     <row r="75">
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.002977568738852354</v>
+        <v>0.002977567899212219</v>
       </c>
       <c r="D75" t="n">
-        <v>0.005687098684252077</v>
+        <v>-0.004285429670475623</v>
       </c>
     </row>
     <row r="76">
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.04205066816097403</v>
+        <v>0.04205067321822553</v>
       </c>
       <c r="D76" t="n">
-        <v>0.008340261276382752</v>
+        <v>-0.003183603158059002</v>
       </c>
     </row>
     <row r="77">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.002367467640633114</v>
+        <v>0.002367590618300275</v>
       </c>
       <c r="D77" t="n">
-        <v>0.005263576413915543</v>
+        <v>-0.004515496986879308</v>
       </c>
     </row>
     <row r="78">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.005290561369752811</v>
+        <v>0.005290499220510503</v>
       </c>
       <c r="D78" t="n">
-        <v>0.007184778140114068</v>
+        <v>-0.001852681141171402</v>
       </c>
     </row>
     <row r="79">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-0.02184866672282937</v>
+        <v>-0.02184860146467726</v>
       </c>
       <c r="D79" t="n">
-        <v>0.007593177534270423</v>
+        <v>-0.002434630122429017</v>
       </c>
     </row>
     <row r="80">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.03403677307189801</v>
+        <v>0.03403663798739631</v>
       </c>
       <c r="D80" t="n">
-        <v>0.008599278337078508</v>
+        <v>-0.006263518275156131</v>
       </c>
     </row>
     <row r="81">
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.06689097860652349</v>
+        <v>0.06689119178775949</v>
       </c>
       <c r="D81" t="n">
-        <v>0.009837818694094598</v>
+        <v>-0.005517289663791424</v>
       </c>
     </row>
     <row r="82">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0.006159577259239102</v>
+        <v>0.006159448938652501</v>
       </c>
       <c r="D82" t="n">
-        <v>0.002299455507790918</v>
+        <v>-0.004281860051827898</v>
       </c>
     </row>
     <row r="83">
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.004933043362475686</v>
+        <v>0.004933153297888571</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.005657628874446467</v>
+        <v>-0.00812462056889195</v>
       </c>
     </row>
     <row r="84">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-0.01048038361463433</v>
+        <v>-0.01048049830837439</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.003851843764322192</v>
+        <v>-0.003103144864720754</v>
       </c>
     </row>
     <row r="85">
@@ -1783,7 +1783,7 @@
         <v>0.01291952520914563</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.002163132941086406</v>
+        <v>-0.008430351644209138</v>
       </c>
     </row>
     <row r="86">
@@ -1799,7 +1799,7 @@
         <v>-0.04584465780199964</v>
       </c>
       <c r="D86" t="n">
-        <v>0.001377422538440299</v>
+        <v>-0.006496876220957662</v>
       </c>
     </row>
     <row r="87">
@@ -1815,7 +1815,7 @@
         <v>0.02269695463173571</v>
       </c>
       <c r="D87" t="n">
-        <v>0.005941463768611334</v>
+        <v>0.003981559109367932</v>
       </c>
     </row>
     <row r="88">
@@ -1831,7 +1831,7 @@
         <v>-0.01143365531757645</v>
       </c>
       <c r="D88" t="n">
-        <v>0.006488920070166288</v>
+        <v>-0.00486972045801712</v>
       </c>
     </row>
     <row r="89">
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.07226274459450099</v>
+        <v>0.07226285016152545</v>
       </c>
       <c r="D89" t="n">
-        <v>0.008065805915937722</v>
+        <v>-0.004471132672887061</v>
       </c>
     </row>
     <row r="90">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>0.02107988789260518</v>
+        <v>0.02107978929631227</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.001028770205499241</v>
+        <v>-0.009927934264395515</v>
       </c>
     </row>
     <row r="91">
@@ -1879,7 +1879,7 @@
         <v>0.01997119977685968</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.0004867438677165891</v>
+        <v>-0.01107578241357958</v>
       </c>
     </row>
     <row r="92">
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0.006525392305332445</v>
+        <v>0.006525299717866417</v>
       </c>
       <c r="D92" t="n">
-        <v>0.000171871327178154</v>
+        <v>-0.007805977581280732</v>
       </c>
     </row>
     <row r="93">
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>0.02534924153682627</v>
+        <v>0.02534943289226488</v>
       </c>
       <c r="D93" t="n">
-        <v>0.003206699370140776</v>
+        <v>-0.01198055488221235</v>
       </c>
     </row>
     <row r="94">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-0.01196203216289859</v>
+        <v>-0.01196212358171678</v>
       </c>
       <c r="D94" t="n">
-        <v>0.008516690980098447</v>
+        <v>-0.007460042930737624</v>
       </c>
     </row>
     <row r="95">
@@ -1943,7 +1943,7 @@
         <v>-0.03324978371014042</v>
       </c>
       <c r="D95" t="n">
-        <v>0.007940860875137496</v>
+        <v>-0.008170409198291463</v>
       </c>
     </row>
     <row r="96">
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-0.05345741284169159</v>
+        <v>-0.05345732072482301</v>
       </c>
       <c r="D96" t="n">
-        <v>0.003930410993989194</v>
+        <v>-0.006952743636490894</v>
       </c>
     </row>
     <row r="97">
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-0.004632432783846507</v>
+        <v>-0.004632614833183779</v>
       </c>
       <c r="D97" t="n">
-        <v>0.005592939544162704</v>
+        <v>-0.004203053592680639</v>
       </c>
     </row>
     <row r="98">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>0.006612696098669879</v>
+        <v>0.00661279889190769</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0143847186142023</v>
+        <v>0.006780814871896489</v>
       </c>
     </row>
     <row r="99">
@@ -2007,7 +2007,7 @@
         <v>0.01671734618909415</v>
       </c>
       <c r="D99" t="n">
-        <v>0.01211557808612572</v>
+        <v>-0.007491874897077691</v>
       </c>
     </row>
     <row r="100">
@@ -2023,7 +2023,7 @@
         <v>-0.02761015298529002</v>
       </c>
       <c r="D100" t="n">
-        <v>0.01127768750941702</v>
+        <v>-0.005723129571638438</v>
       </c>
     </row>
     <row r="101">
@@ -2039,7 +2039,7 @@
         <v>0.0621731555095586</v>
       </c>
       <c r="D101" t="n">
-        <v>0.01371438040800161</v>
+        <v>0.0005359375288519945</v>
       </c>
     </row>
     <row r="102">
@@ -2055,7 +2055,7 @@
         <v>0.01411632462637091</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.0008174120346624821</v>
+        <v>-0.01252737026862096</v>
       </c>
     </row>
     <row r="103">
@@ -2071,7 +2071,7 @@
         <v>-0.0365779617540315</v>
       </c>
       <c r="D103" t="n">
-        <v>0.001159401077921259</v>
+        <v>-0.01228971032822879</v>
       </c>
     </row>
     <row r="104">
@@ -2087,7 +2087,7 @@
         <v>0.05912742494696221</v>
       </c>
       <c r="D104" t="n">
-        <v>0.00315369166728683</v>
+        <v>-0.00240540842064798</v>
       </c>
     </row>
     <row r="105">
@@ -2103,7 +2103,7 @@
         <v>0.0006127718879815891</v>
       </c>
       <c r="D105" t="n">
-        <v>0.003611719755046114</v>
+        <v>-0.01036556397393676</v>
       </c>
     </row>
     <row r="106">
@@ -2119,7 +2119,7 @@
         <v>-0.03331257861273373</v>
       </c>
       <c r="D106" t="n">
-        <v>0.006680417970283639</v>
+        <v>-0.004329374155627841</v>
       </c>
     </row>
     <row r="107">
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-0.001966891776348234</v>
+        <v>-0.001966959189177775</v>
       </c>
       <c r="D107" t="n">
-        <v>0.007120515398241668</v>
+        <v>0.0007985113964434605</v>
       </c>
     </row>
     <row r="108">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.05636810712767559</v>
+        <v>0.05636803826638181</v>
       </c>
       <c r="D108" t="n">
-        <v>0.007264799462885101</v>
+        <v>0.0005109909887539886</v>
       </c>
     </row>
     <row r="109">
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.1136965007997019</v>
+        <v>0.1136963770673936</v>
       </c>
       <c r="D109" t="n">
-        <v>0.005294232994578235</v>
+        <v>0.005840012319302196</v>
       </c>
     </row>
     <row r="110">
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.08287199715371019</v>
+        <v>0.0828721135181496</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.003007109553173359</v>
+        <v>-0.011950440281315</v>
       </c>
     </row>
     <row r="111">
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-0.05029756641243965</v>
+        <v>-0.05029777076089303</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.005180817626650365</v>
+        <v>-0.01376259652493444</v>
       </c>
     </row>
     <row r="112">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-0.01114607549135349</v>
+        <v>-0.01114577136481321</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.0005196827463513345</v>
+        <v>-0.008081317815018613</v>
       </c>
     </row>
     <row r="113">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-0.002328794652284971</v>
+        <v>-0.002329006976091286</v>
       </c>
       <c r="D113" t="n">
-        <v>0.008339384616133996</v>
+        <v>-0.001337517886643867</v>
       </c>
     </row>
     <row r="114">
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.02925576278695285</v>
+        <v>0.02925598737139057</v>
       </c>
       <c r="D114" t="n">
-        <v>0.01263897756729514</v>
+        <v>0.002155825029193639</v>
       </c>
     </row>
     <row r="115">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>0.02407484260203807</v>
+        <v>0.02407484401681059</v>
       </c>
       <c r="D115" t="n">
-        <v>0.007266630839723455</v>
+        <v>-0.002073909498323995</v>
       </c>
     </row>
     <row r="116">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.04727146704585516</v>
+        <v>0.04727112010430412</v>
       </c>
       <c r="D116" t="n">
-        <v>0.00834725307679115</v>
+        <v>-0.007316395266614855</v>
       </c>
     </row>
     <row r="117">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-0.002269571872295151</v>
+        <v>-0.002269458676002367</v>
       </c>
       <c r="D117" t="n">
-        <v>0.001342462152450898</v>
+        <v>-0.007887575779710524</v>
       </c>
     </row>
     <row r="118">
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-0.02069542831744564</v>
+        <v>-0.02069524720311677</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.003967534355286308</v>
+        <v>-0.007532165531520826</v>
       </c>
     </row>
     <row r="119">
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.03584390885074851</v>
+        <v>0.03584380553157751</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.00146515562154724</v>
+        <v>0.002351412572931044</v>
       </c>
     </row>
     <row r="120">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-0.02084626761109032</v>
+        <v>-0.02084617848271142</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.002708555516658756</v>
+        <v>-0.007399920430840781</v>
       </c>
     </row>
     <row r="121">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0.07378845972678261</v>
+        <v>0.07378845184664962</v>
       </c>
       <c r="D121" t="n">
-        <v>0.001958562884491949</v>
+        <v>-0.005042188551550406</v>
       </c>
     </row>
     <row r="122">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.008713678985844187</v>
+        <v>0.008713514010066925</v>
       </c>
       <c r="D122" t="n">
-        <v>6.37249375572595e-05</v>
+        <v>-0.002683445396276029</v>
       </c>
     </row>
     <row r="123">
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>0.005337785270540962</v>
+        <v>0.005337943051587857</v>
       </c>
       <c r="D123" t="n">
-        <v>0.003292683610232195</v>
+        <v>-0.007689482189179961</v>
       </c>
     </row>
     <row r="124">
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>-0.05869351950675505</v>
+        <v>-0.0586935959020296</v>
       </c>
       <c r="D124" t="n">
-        <v>0.002622493086346318</v>
+        <v>-0.004907882688245694</v>
       </c>
     </row>
     <row r="125">
@@ -2423,7 +2423,7 @@
         <v>-0.01822339328045142</v>
       </c>
       <c r="D125" t="n">
-        <v>0.004670067810365459</v>
+        <v>-0.005914931125970666</v>
       </c>
     </row>
     <row r="126">
@@ -2439,7 +2439,7 @@
         <v>0.04359039950178656</v>
       </c>
       <c r="D126" t="n">
-        <v>0.006337917274237178</v>
+        <v>-0.004696966423818321</v>
       </c>
     </row>
     <row r="127">
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-0.06831257628917098</v>
+        <v>-0.06831249532921913</v>
       </c>
       <c r="D127" t="n">
-        <v>0.006692055221295756</v>
+        <v>-0.0035106505366903</v>
       </c>
     </row>
     <row r="128">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.004106820744502415</v>
+        <v>0.004106731399656671</v>
       </c>
       <c r="D128" t="n">
-        <v>0.007231651783743128</v>
+        <v>-0.003177625485930251</v>
       </c>
     </row>
     <row r="129">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>-0.0182092437137743</v>
+        <v>-0.01820915308173721</v>
       </c>
       <c r="D129" t="n">
-        <v>0.0117385892919993</v>
+        <v>-0.005021619701020304</v>
       </c>
     </row>
     <row r="130">
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0.02727629467241433</v>
+        <v>0.02727619159044625</v>
       </c>
       <c r="D130" t="n">
-        <v>0.01249073269286998</v>
+        <v>-0.008144458112035902</v>
       </c>
     </row>
     <row r="131">
@@ -2519,7 +2519,7 @@
         <v>-0.03880891099822015</v>
       </c>
       <c r="D131" t="n">
-        <v>0.002461485763503123</v>
+        <v>-0.006182269860100235</v>
       </c>
     </row>
     <row r="132">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>-0.04312248372520633</v>
+        <v>-0.04312239735821066</v>
       </c>
       <c r="D132" t="n">
-        <v>0.002528168267091035</v>
+        <v>-0.0041011331283118</v>
       </c>
     </row>
     <row r="133">
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>-0.02613984328111862</v>
+        <v>-0.02614003634793316</v>
       </c>
       <c r="D133" t="n">
-        <v>0.01275358581709216</v>
+        <v>0.006733993966750896</v>
       </c>
     </row>
     <row r="134">
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.001563336553968897</v>
+        <v>0.001563443623350036</v>
       </c>
       <c r="D134" t="n">
-        <v>0.01463196512007567</v>
+        <v>-0.006073934219950261</v>
       </c>
     </row>
     <row r="135">
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>-0.005804948443033253</v>
+        <v>-0.0058048469347316</v>
       </c>
       <c r="D135" t="n">
-        <v>0.01511920682274748</v>
+        <v>-0.003161314476135484</v>
       </c>
     </row>
     <row r="136">
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>-0.05728155693409609</v>
+        <v>-0.05728155462718387</v>
       </c>
       <c r="D136" t="n">
-        <v>0.01487494481616524</v>
+        <v>0.002602443833660989</v>
       </c>
     </row>
     <row r="137">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>-0.006983788939213476</v>
+        <v>-0.006983894624855491</v>
       </c>
       <c r="D137" t="n">
-        <v>0.004198258621908274</v>
+        <v>-0.007979070786399596</v>
       </c>
     </row>
     <row r="138">
@@ -2631,7 +2631,7 @@
         <v>0.0381882811104779</v>
       </c>
       <c r="D138" t="n">
-        <v>0.006439457984639472</v>
+        <v>-0.0122210397657596</v>
       </c>
     </row>
     <row r="139">
@@ -2647,7 +2647,7 @@
         <v>-0.02200810561130795</v>
       </c>
       <c r="D139" t="n">
-        <v>0.006078900678695081</v>
+        <v>-0.00563209915145497</v>
       </c>
     </row>
     <row r="140">
@@ -2663,7 +2663,7 @@
         <v>-0.007168618633277557</v>
       </c>
       <c r="D140" t="n">
-        <v>0.004833113137619102</v>
+        <v>-0.005450509508016918</v>
       </c>
     </row>
     <row r="141">
@@ -2679,7 +2679,7 @@
         <v>0.002367806409754758</v>
       </c>
       <c r="D141" t="n">
-        <v>0.007309610596929084</v>
+        <v>-0.0054557694687958</v>
       </c>
     </row>
     <row r="142">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>-0.003253727850250465</v>
+        <v>-0.003253637781160279</v>
       </c>
       <c r="D142" t="n">
-        <v>0.007101515935606208</v>
+        <v>0.004636107587173004</v>
       </c>
     </row>
     <row r="143">
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.05118353272635656</v>
+        <v>0.05118352828023132</v>
       </c>
       <c r="D143" t="n">
-        <v>0.007091282837455169</v>
+        <v>0.0001098980990058103</v>
       </c>
     </row>
     <row r="144">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.02606500479224771</v>
+        <v>0.02606491580810077</v>
       </c>
       <c r="D144" t="n">
-        <v>0.00695172894853757</v>
+        <v>0.004097596946272678</v>
       </c>
     </row>
     <row r="145">
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.05837466326432628</v>
+        <v>0.05837458210911772</v>
       </c>
       <c r="D145" t="n">
-        <v>0.001177061269251203</v>
+        <v>-0.004452407382973936</v>
       </c>
     </row>
     <row r="146">
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>-0.0509856289214754</v>
+        <v>-0.05098555244726655</v>
       </c>
       <c r="D146" t="n">
-        <v>3.53796375012292e-05</v>
+        <v>-0.01323106331440334</v>
       </c>
     </row>
     <row r="147">
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>-0.001598203623107475</v>
+        <v>-0.001598124407650947</v>
       </c>
       <c r="D147" t="n">
-        <v>0.0044965826074523</v>
+        <v>-0.006401606699394376</v>
       </c>
     </row>
     <row r="148">
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0.0225653569397114</v>
+        <v>0.02256519464703488</v>
       </c>
       <c r="D148" t="n">
-        <v>0.009034688048511472</v>
+        <v>-0.0008254923972791806</v>
       </c>
     </row>
     <row r="149">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.0107126552975465</v>
+        <v>0.01071265507818175</v>
       </c>
       <c r="D149" t="n">
-        <v>0.01113814891245122</v>
+        <v>-0.001369422356789819</v>
       </c>
     </row>
     <row r="150">
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>-0.02171003324077625</v>
+        <v>-0.0217099558599545</v>
       </c>
       <c r="D150" t="n">
-        <v>0.006559704956136649</v>
+        <v>-0.004139968667785116</v>
       </c>
     </row>
     <row r="151">
@@ -2839,7 +2839,7 @@
         <v>-0.1203626575226986</v>
       </c>
       <c r="D151" t="n">
-        <v>0.01010063025026052</v>
+        <v>-0.004703361164627669</v>
       </c>
     </row>
     <row r="152">
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>-0.06452962664157669</v>
+        <v>-0.0645297180759079</v>
       </c>
       <c r="D152" t="n">
-        <v>0.01165637401834212</v>
+        <v>0.000372057407131132</v>
       </c>
     </row>
     <row r="153">
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0.04651759168215663</v>
+        <v>0.0465176848810479</v>
       </c>
       <c r="D153" t="n">
-        <v>0.008290198186192671</v>
+        <v>0.002102641531323146</v>
       </c>
     </row>
     <row r="154">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>-0.08673338492859328</v>
+        <v>-0.08673329694028231</v>
       </c>
       <c r="D154" t="n">
-        <v>0.005768263469355666</v>
+        <v>0.002702466285211217</v>
       </c>
     </row>
     <row r="155">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>0.06747424583979256</v>
+        <v>0.06747414493398929</v>
       </c>
       <c r="D155" t="n">
-        <v>0.00252146661462049</v>
+        <v>-0.0008970808697870564</v>
       </c>
     </row>
     <row r="156">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0.1356332624169982</v>
+        <v>0.1356331781314846</v>
       </c>
       <c r="D156" t="n">
-        <v>0.0004932039322239319</v>
+        <v>-0.01004207669137315</v>
       </c>
     </row>
     <row r="157">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>-0.03570967130249925</v>
+        <v>-0.03570959930889706</v>
       </c>
       <c r="D157" t="n">
-        <v>-0.001162942787479584</v>
+        <v>-0.009318973864670656</v>
       </c>
     </row>
     <row r="158">
@@ -2951,7 +2951,7 @@
         <v>0.02426155435430633</v>
       </c>
       <c r="D158" t="n">
-        <v>-0.001409003773975927</v>
+        <v>-0.002007028363045452</v>
       </c>
     </row>
     <row r="159">
@@ -2967,7 +2967,7 @@
         <v>0.005851701148207322</v>
       </c>
       <c r="D159" t="n">
-        <v>0.001006447196172244</v>
+        <v>-0.006995257030684824</v>
       </c>
     </row>
     <row r="160">
@@ -2983,7 +2983,7 @@
         <v>0.05689017199292679</v>
       </c>
       <c r="D160" t="n">
-        <v>0.002933951133020485</v>
+        <v>-0.01254717294607974</v>
       </c>
     </row>
     <row r="161">
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>-0.1306087790032808</v>
+        <v>-0.1306087103919212</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.0007132623803396947</v>
+        <v>-0.0080607823997744</v>
       </c>
     </row>
     <row r="162">
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>-0.0004591520635843782</v>
+        <v>-0.0004591495365557918</v>
       </c>
       <c r="D162" t="n">
-        <v>0.008227851598012738</v>
+        <v>0.002869082107557577</v>
       </c>
     </row>
     <row r="163">
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>-0.02132169210410606</v>
+        <v>-0.02132185044215507</v>
       </c>
       <c r="D163" t="n">
-        <v>0.008620352928524901</v>
+        <v>-0.005844213239872758</v>
       </c>
     </row>
     <row r="164">
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>-0.004431138021629089</v>
+        <v>-0.004430973032743535</v>
       </c>
       <c r="D164" t="n">
-        <v>0.01759777116291461</v>
+        <v>-0.002667000748171129</v>
       </c>
     </row>
     <row r="165">
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>0.007135653717280865</v>
+        <v>0.007135562132345896</v>
       </c>
       <c r="D165" t="n">
-        <v>0.00999173417154217</v>
+        <v>-0.004647533654982227</v>
       </c>
     </row>
     <row r="166">
@@ -3079,7 +3079,7 @@
         <v>0.01657698351176395</v>
       </c>
       <c r="D166" t="n">
-        <v>0.00387503589595655</v>
+        <v>-0.008813567080167289</v>
       </c>
     </row>
     <row r="167">
@@ -3095,7 +3095,7 @@
         <v>-0.01584539256568596</v>
       </c>
       <c r="D167" t="n">
-        <v>0.0003484044633419916</v>
+        <v>-0.00890907267606344</v>
       </c>
     </row>
     <row r="168">
@@ -3111,7 +3111,7 @@
         <v>-0.01775229044331095</v>
       </c>
       <c r="D168" t="n">
-        <v>0.009973606108903195</v>
+        <v>0.00378559284658279</v>
       </c>
     </row>
     <row r="169">
@@ -3127,7 +3127,7 @@
         <v>-0.04155804926479112</v>
       </c>
       <c r="D169" t="n">
-        <v>0.01058351411225821</v>
+        <v>-0.006308757952722789</v>
       </c>
     </row>
     <row r="170">
@@ -3143,7 +3143,7 @@
         <v>-0.03315174651899633</v>
       </c>
       <c r="D170" t="n">
-        <v>0.01545076174199253</v>
+        <v>-0.004463482914785519</v>
       </c>
     </row>
     <row r="171">
@@ -3159,7 +3159,7 @@
         <v>0.06841357297928297</v>
       </c>
       <c r="D171" t="n">
-        <v>0.01763528426597672</v>
+        <v>0.004694901610153623</v>
       </c>
     </row>
     <row r="172">
@@ -3175,7 +3175,7 @@
         <v>0.01527469810905324</v>
       </c>
       <c r="D172" t="n">
-        <v>0.001742659907904488</v>
+        <v>-0.01187050850095677</v>
       </c>
     </row>
     <row r="173">
@@ -3191,7 +3191,7 @@
         <v>-0.07559693090430453</v>
       </c>
       <c r="D173" t="n">
-        <v>0.001076823062626491</v>
+        <v>-0.01155942423414018</v>
       </c>
     </row>
     <row r="174">
@@ -3207,7 +3207,7 @@
         <v>0.05520824709784722</v>
       </c>
       <c r="D174" t="n">
-        <v>0.004559644277685053</v>
+        <v>-0.001494448294855964</v>
       </c>
     </row>
     <row r="175">
@@ -3223,7 +3223,7 @@
         <v>0.1183235159556704</v>
       </c>
       <c r="D175" t="n">
-        <v>0.005469406364845887</v>
+        <v>-0.008808679406218118</v>
       </c>
     </row>
     <row r="176">
@@ -3239,7 +3239,7 @@
         <v>-0.06044235589280234</v>
       </c>
       <c r="D176" t="n">
-        <v>0.003355745750646189</v>
+        <v>-0.007867017762954995</v>
       </c>
     </row>
     <row r="177">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>-0.05059219173499796</v>
+        <v>-0.05059204909035009</v>
       </c>
       <c r="D177" t="n">
-        <v>0.009876912795042537</v>
+        <v>0.007914324776574021</v>
       </c>
     </row>
     <row r="178">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>0.06936493400878407</v>
+        <v>0.06936485332263698</v>
       </c>
       <c r="D178" t="n">
-        <v>0.01068843686970659</v>
+        <v>-0.001288450435683118</v>
       </c>
     </row>
     <row r="179">
@@ -3284,10 +3284,10 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>-0.0908610379529039</v>
+        <v>-0.09086110868916941</v>
       </c>
       <c r="D179" t="n">
-        <v>0.007344748498604132</v>
+        <v>0.004248757868170335</v>
       </c>
     </row>
     <row r="180">
@@ -3300,10 +3300,10 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0.01125261655338139</v>
+        <v>0.01125261621612061</v>
       </c>
       <c r="D180" t="n">
-        <v>0.007672468158267895</v>
+        <v>0.003617513235233578</v>
       </c>
     </row>
     <row r="181">
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>0.00727458896509825</v>
+        <v>0.007274821231171513</v>
       </c>
       <c r="D181" t="n">
-        <v>0.006521163801163918</v>
+        <v>-0.002910777919418591</v>
       </c>
     </row>
     <row r="182">
@@ -3332,10 +3332,10 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>-0.06897084462497027</v>
+        <v>-0.06897097753075099</v>
       </c>
       <c r="D182" t="n">
-        <v>0.009200311133298462</v>
+        <v>-0.005975305712593677</v>
       </c>
     </row>
     <row r="183">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>0.0944421460129754</v>
+        <v>0.09444198391736425</v>
       </c>
       <c r="D183" t="n">
-        <v>0.01153508507827549</v>
+        <v>0.004365489860895214</v>
       </c>
     </row>
     <row r="184">
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>-0.01540347317882118</v>
+        <v>-0.01540324926588277</v>
       </c>
       <c r="D184" t="n">
-        <v>0.008347408025211105</v>
+        <v>-0.003596521072173417</v>
       </c>
     </row>
     <row r="185">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>-0.02527854573283994</v>
+        <v>-0.0252785408549836</v>
       </c>
       <c r="D185" t="n">
-        <v>0.007520655273244229</v>
+        <v>-0.005183474816866596</v>
       </c>
     </row>
     <row r="186">
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>-0.03648270559179179</v>
+        <v>-0.0364827088498163</v>
       </c>
       <c r="D186" t="n">
-        <v>0.008224607907973382</v>
+        <v>-0.001249593718186298</v>
       </c>
     </row>
     <row r="187">
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>0.1403608179160061</v>
+        <v>0.1403606398184005</v>
       </c>
       <c r="D187" t="n">
-        <v>0.009246645697324071</v>
+        <v>-0.00394314549531582</v>
       </c>
     </row>
     <row r="188">
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>-0.0679140324032742</v>
+        <v>-0.06791403804770668</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.004390955309720382</v>
+        <v>-0.008468122530712155</v>
       </c>
     </row>
     <row r="189">
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>-0.0668088374138347</v>
+        <v>-0.06680876691220328</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.001983497150710731</v>
+        <v>0.006490439441642786</v>
       </c>
     </row>
     <row r="190">
@@ -3463,7 +3463,7 @@
         <v>-0.001612153856708876</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.00238659504760685</v>
+        <v>-0.00133522942288233</v>
       </c>
     </row>
     <row r="191">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>-0.01668835150760095</v>
+        <v>-0.01668827901223435</v>
       </c>
       <c r="D191" t="n">
-        <v>0.007767188081290899</v>
+        <v>-0.008717694570511539</v>
       </c>
     </row>
     <row r="192">
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0.1300423732385285</v>
+        <v>0.130042362441656</v>
       </c>
       <c r="D192" t="n">
-        <v>0.007795773490198084</v>
+        <v>0.00608858791888763</v>
       </c>
     </row>
     <row r="193">
@@ -3508,10 +3508,10 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.03219737245751264</v>
+        <v>0.03219724484643294</v>
       </c>
       <c r="D193" t="n">
-        <v>0.001065670926549681</v>
+        <v>-0.006955165047846646</v>
       </c>
     </row>
     <row r="194">
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.09785288195042785</v>
+        <v>0.09785295102028857</v>
       </c>
       <c r="D194" t="n">
-        <v>5.642303837621356e-05</v>
+        <v>-0.009877933700395613</v>
       </c>
     </row>
     <row r="195">
@@ -3543,7 +3543,7 @@
         <v>0.04962294311756776</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.008879587736060148</v>
+        <v>-0.01706107000493641</v>
       </c>
     </row>
     <row r="196">
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>-0.009127592975432419</v>
+        <v>-0.009127486284240982</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.004833710540482215</v>
+        <v>-0.01664844443125229</v>
       </c>
     </row>
     <row r="197">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>0.2125699310596795</v>
+        <v>0.2125698054309869</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.0009412526902932037</v>
+        <v>-0.00544827467882655</v>
       </c>
     </row>
     <row r="198">
@@ -3591,7 +3591,7 @@
         <v>0.007861715420208859</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.005930109242538767</v>
+        <v>-0.01695927190409836</v>
       </c>
     </row>
     <row r="199">
@@ -3607,7 +3607,7 @@
         <v>0.02575612528412585</v>
       </c>
       <c r="D199" t="n">
-        <v>0.001426575956252289</v>
+        <v>-0.01020066201612339</v>
       </c>
     </row>
     <row r="200">
@@ -3623,7 +3623,7 @@
         <v>-0.1424557307837516</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.002120188245402535</v>
+        <v>-0.008177680487854387</v>
       </c>
     </row>
     <row r="201">
@@ -3639,7 +3639,7 @@
         <v>0.03099531558400925</v>
       </c>
       <c r="D201" t="n">
-        <v>0.00788658975577129</v>
+        <v>-0.006504044718041219</v>
       </c>
     </row>
     <row r="202">
@@ -3655,7 +3655,7 @@
         <v>-0.01890396702562758</v>
       </c>
       <c r="D202" t="n">
-        <v>0.005016469372672727</v>
+        <v>-0.0007007398847490099</v>
       </c>
     </row>
     <row r="203">
@@ -3671,7 +3671,7 @@
         <v>0.07168836558821046</v>
       </c>
       <c r="D203" t="n">
-        <v>0.01611990659613181</v>
+        <v>0.01094726120845462</v>
       </c>
     </row>
     <row r="204">
@@ -3687,7 +3687,7 @@
         <v>-0.02423473037313673</v>
       </c>
       <c r="D204" t="n">
-        <v>0.0061015468126141</v>
+        <v>-0.007801189325781398</v>
       </c>
     </row>
     <row r="205">
@@ -3703,7 +3703,7 @@
         <v>-0.005609709268098007</v>
       </c>
       <c r="D205" t="n">
-        <v>0.01083962775086544</v>
+        <v>-0.008962864044215773</v>
       </c>
     </row>
     <row r="206">
@@ -3719,7 +3719,7 @@
         <v>-0.1533166961150667</v>
       </c>
       <c r="D206" t="n">
-        <v>0.01166353144324732</v>
+        <v>0.0002102275945074185</v>
       </c>
     </row>
     <row r="207">
@@ -3735,7 +3735,7 @@
         <v>0.03781549378761184</v>
       </c>
       <c r="D207" t="n">
-        <v>0.009606742282658873</v>
+        <v>-0.0009607936433394292</v>
       </c>
     </row>
     <row r="208">
@@ -3751,7 +3751,7 @@
         <v>0.03892671989335472</v>
       </c>
       <c r="D208" t="n">
-        <v>0.008708916703404195</v>
+        <v>-0.002842480368938532</v>
       </c>
     </row>
     <row r="209">
@@ -3767,7 +3767,7 @@
         <v>0.1915717571808606</v>
       </c>
       <c r="D209" t="n">
-        <v>0.008324206690224139</v>
+        <v>-0.003812103397434614</v>
       </c>
     </row>
     <row r="210">
@@ -3783,7 +3783,7 @@
         <v>-0.05675013211859026</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.006688233825374282</v>
+        <v>-0.01360763430973569</v>
       </c>
     </row>
     <row r="211">
@@ -3799,7 +3799,7 @@
         <v>-0.03941933700193168</v>
       </c>
       <c r="D211" t="n">
-        <v>-1.520951616589255e-05</v>
+        <v>-0.00943195235054139</v>
       </c>
     </row>
     <row r="212">
@@ -3815,7 +3815,7 @@
         <v>-0.03882697609539476</v>
       </c>
       <c r="D212" t="n">
-        <v>0.00492773775770657</v>
+        <v>-0.0003930246437759992</v>
       </c>
     </row>
     <row r="213">
@@ -3831,7 +3831,7 @@
         <v>0.02459300890354377</v>
       </c>
       <c r="D213" t="n">
-        <v>0.006166474600868201</v>
+        <v>0.00136119301550806</v>
       </c>
     </row>
     <row r="214">
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>-0.03788694487961641</v>
+        <v>-0.03788700939259471</v>
       </c>
       <c r="D214" t="n">
-        <v>0.004251472686497214</v>
+        <v>0.006015593181231254</v>
       </c>
     </row>
     <row r="215">
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>0.09338503739313642</v>
+        <v>0.09338510810859968</v>
       </c>
       <c r="D215" t="n">
-        <v>0.006784642829443752</v>
+        <v>-0.004079168806582862</v>
       </c>
     </row>
     <row r="216">
@@ -3879,7 +3879,7 @@
         <v>0.02171558815195085</v>
       </c>
       <c r="D216" t="n">
-        <v>0.002504546622448912</v>
+        <v>-0.006692197584083253</v>
       </c>
     </row>
     <row r="217">
@@ -3895,7 +3895,7 @@
         <v>-0.2064814846515958</v>
       </c>
       <c r="D217" t="n">
-        <v>0.002550863584152523</v>
+        <v>-0.008700502585684609</v>
       </c>
     </row>
     <row r="218">
@@ -3911,7 +3911,7 @@
         <v>-0.01032407518355138</v>
       </c>
       <c r="D218" t="n">
-        <v>0.01335530857484501</v>
+        <v>0.01368045320208222</v>
       </c>
     </row>
     <row r="219">
@@ -3927,7 +3927,7 @@
         <v>-0.03278127523246044</v>
       </c>
       <c r="D219" t="n">
-        <v>0.01847785140752829</v>
+        <v>0.006831427915110122</v>
       </c>
     </row>
     <row r="220">
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0.008275352638766442</v>
+        <v>0.00827543466400904</v>
       </c>
       <c r="D220" t="n">
-        <v>0.01906588279700026</v>
+        <v>0.00360147078948751</v>
       </c>
     </row>
     <row r="221">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>0.08108535898685787</v>
+        <v>0.08108526131660088</v>
       </c>
       <c r="D221" t="n">
-        <v>0.01216365962833719</v>
+        <v>0.001180736201392776</v>
       </c>
     </row>
     <row r="222">
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>0.07877530872806959</v>
+        <v>0.07877523571075074</v>
       </c>
       <c r="D222" t="n">
-        <v>0.003299874905538755</v>
+        <v>-0.008456448392494521</v>
       </c>
     </row>
     <row r="223">
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>-0.04012772476002968</v>
+        <v>-0.04012766507099674</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.008372084388285395</v>
+        <v>-0.01531863643080275</v>
       </c>
     </row>
     <row r="224">
@@ -4007,7 +4007,7 @@
         <v>0.02364789640770582</v>
       </c>
       <c r="D224" t="n">
-        <v>-0.00570817735066708</v>
+        <v>0.001000437737989712</v>
       </c>
     </row>
     <row r="225">
@@ -4023,7 +4023,7 @@
         <v>0.01739957857315111</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.004905803032612195</v>
+        <v>-0.00842628243121738</v>
       </c>
     </row>
     <row r="226">
@@ -4039,7 +4039,7 @@
         <v>-0.0926780408255683</v>
       </c>
       <c r="D226" t="n">
-        <v>0.001664322169554336</v>
+        <v>-0.007183421159322788</v>
       </c>
     </row>
     <row r="227">
@@ -4055,7 +4055,7 @@
         <v>-0.03193541327102667</v>
       </c>
       <c r="D227" t="n">
-        <v>0.006307180556661853</v>
+        <v>0.009243615933065793</v>
       </c>
     </row>
     <row r="228">
@@ -4071,7 +4071,7 @@
         <v>0.05193453306366003</v>
       </c>
       <c r="D228" t="n">
-        <v>0.0108012706776099</v>
+        <v>-0.002821347957452624</v>
       </c>
     </row>
     <row r="229">
@@ -4087,7 +4087,7 @@
         <v>-0.1045305031723139</v>
       </c>
       <c r="D229" t="n">
-        <v>0.009759767511438774</v>
+        <v>-0.004937814151435755</v>
       </c>
     </row>
     <row r="230">
@@ -4103,7 +4103,7 @@
         <v>-0.03157327065710047</v>
       </c>
       <c r="D230" t="n">
-        <v>0.006443698074543411</v>
+        <v>0.001131830262971781</v>
       </c>
     </row>
     <row r="231">
@@ -4119,7 +4119,7 @@
         <v>0.02825863666630446</v>
       </c>
       <c r="D231" t="n">
-        <v>0.006897721285365749</v>
+        <v>-0.003134410852910829</v>
       </c>
     </row>
     <row r="232">
@@ -4135,7 +4135,7 @@
         <v>-0.05610132739586904</v>
       </c>
       <c r="D232" t="n">
-        <v>0.01000543483315358</v>
+        <v>-0.005093734177418204</v>
       </c>
     </row>
     <row r="233">
@@ -4151,7 +4151,7 @@
         <v>-0.05544664186528636</v>
       </c>
       <c r="D233" t="n">
-        <v>0.00796398762081791</v>
+        <v>-0.001086935277992972</v>
       </c>
     </row>
     <row r="234">
@@ -4167,7 +4167,7 @@
         <v>0.1484411058018817</v>
       </c>
       <c r="D234" t="n">
-        <v>0.01452531112468093</v>
+        <v>-0.00172905089334996</v>
       </c>
     </row>
     <row r="235">
@@ -4183,7 +4183,7 @@
         <v>0.1517952164156169</v>
       </c>
       <c r="D235" t="n">
-        <v>0.0071858421284042</v>
+        <v>-0.01378964010085527</v>
       </c>
     </row>
     <row r="236">
@@ -4199,7 +4199,7 @@
         <v>-0.07545029450587093</v>
       </c>
       <c r="D236" t="n">
-        <v>-0.007837028329046453</v>
+        <v>-0.01337956202353412</v>
       </c>
     </row>
     <row r="237">
@@ -4215,7 +4215,7 @@
         <v>-0.04438443475503795</v>
       </c>
       <c r="D237" t="n">
-        <v>-0.008789103443512542</v>
+        <v>-0.005498978123190815</v>
       </c>
     </row>
     <row r="238">
@@ -4231,7 +4231,7 @@
         <v>-0.09755565462613547</v>
       </c>
       <c r="D238" t="n">
-        <v>0.008902329503132658</v>
+        <v>0.003801171957451483</v>
       </c>
     </row>
     <row r="239">
@@ -4247,7 +4247,7 @@
         <v>0.007243447943663828</v>
       </c>
       <c r="D239" t="n">
-        <v>0.01949270744601156</v>
+        <v>-0.001884489922212943</v>
       </c>
     </row>
     <row r="240">
@@ -4263,7 +4263,7 @@
         <v>-0.01388920486527323</v>
       </c>
       <c r="D240" t="n">
-        <v>0.01809817555921974</v>
+        <v>0.004800175428026121</v>
       </c>
     </row>
     <row r="241">
@@ -4279,7 +4279,7 @@
         <v>0.09969492297603466</v>
       </c>
       <c r="D241" t="n">
-        <v>0.01815725903081187</v>
+        <v>0.006397498215294769</v>
       </c>
     </row>
     <row r="242">
@@ -4295,7 +4295,7 @@
         <v>-0.04177863283041472</v>
       </c>
       <c r="D242" t="n">
-        <v>-0.002674611491491479</v>
+        <v>-0.01460565748308097</v>
       </c>
     </row>
     <row r="243">
@@ -4311,7 +4311,7 @@
         <v>0.04804410740144371</v>
       </c>
       <c r="D243" t="n">
-        <v>0.001366257331570817</v>
+        <v>-0.0129422732190433</v>
       </c>
     </row>
     <row r="244">
@@ -4327,7 +4327,7 @@
         <v>0.002396960176923146</v>
       </c>
       <c r="D244" t="n">
-        <v>0.0002080161554231371</v>
+        <v>-0.006822276795250277</v>
       </c>
     </row>
     <row r="245">
@@ -4343,7 +4343,7 @@
         <v>-0.06024786962053807</v>
       </c>
       <c r="D245" t="n">
-        <v>0.004856854652901423</v>
+        <v>-0.007098431242153586</v>
       </c>
     </row>
     <row r="246">
@@ -4359,7 +4359,7 @@
         <v>-0.04230137516860877</v>
       </c>
       <c r="D246" t="n">
-        <v>0.008146345945624495</v>
+        <v>0.002791418749011178</v>
       </c>
     </row>
     <row r="247">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>0.01776499410108712</v>
+        <v>0.01776520567574202</v>
       </c>
       <c r="D247" t="n">
-        <v>0.001202169747623735</v>
+        <v>-0.007834681776494825</v>
       </c>
     </row>
     <row r="248">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>0.1208566633677917</v>
+        <v>0.1208566553531065</v>
       </c>
       <c r="D248" t="n">
-        <v>-0.0002182532253812257</v>
+        <v>-0.001532989062167199</v>
       </c>
     </row>
     <row r="249">
@@ -4404,10 +4404,10 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>-0.007123083531185515</v>
+        <v>-0.007123383886564971</v>
       </c>
       <c r="D249" t="n">
-        <v>-0.004654685718095574</v>
+        <v>-0.002177111947084979</v>
       </c>
     </row>
     <row r="250">
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>-0.06014296444609035</v>
+        <v>-0.06014280512428027</v>
       </c>
       <c r="D250" t="n">
-        <v>-0.001379773387918989</v>
+        <v>-0.01120418079408269</v>
       </c>
     </row>
     <row r="251">
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>0.3337166301897103</v>
+        <v>0.3337168454528217</v>
       </c>
       <c r="D251" t="n">
-        <v>0.003682858372392208</v>
+        <v>0.0007522982601600326</v>
       </c>
     </row>
     <row r="252">
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>-0.01971972044185111</v>
+        <v>-0.01971971621002777</v>
       </c>
       <c r="D252" t="n">
-        <v>-0.005863324155358012</v>
+        <v>-0.01654427824235105</v>
       </c>
     </row>
     <row r="253">
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>-0.02331356689037256</v>
+        <v>-0.02331375762027343</v>
       </c>
       <c r="D253" t="n">
-        <v>-0.001995135417620874</v>
+        <v>0.001480141042279076</v>
       </c>
     </row>
     <row r="254">
@@ -4484,10 +4484,10 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>-0.05838149806505777</v>
+        <v>-0.05838129869154307</v>
       </c>
       <c r="D254" t="n">
-        <v>-0.003121465818532011</v>
+        <v>0.006146976746012281</v>
       </c>
     </row>
     <row r="255">
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>-0.002648929123382548</v>
+        <v>-0.002649036101263769</v>
       </c>
       <c r="D255" t="n">
-        <v>0.01247759354959471</v>
+        <v>-0.0116797847668145</v>
       </c>
     </row>
     <row r="256">
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>0.07204263575935421</v>
+        <v>0.07204275174698482</v>
       </c>
       <c r="D256" t="n">
-        <v>0.01436523900957339</v>
+        <v>0.002754806990244184</v>
       </c>
     </row>
     <row r="257">
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>-0.02229182719177869</v>
+        <v>-0.02229193351827785</v>
       </c>
       <c r="D257" t="n">
-        <v>0.005325966045962052</v>
+        <v>0.00400232393341418</v>
       </c>
     </row>
     <row r="258">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>-0.1476530937240069</v>
+        <v>-0.1476529015506511</v>
       </c>
       <c r="D258" t="n">
-        <v>-0.002990449114310186</v>
+        <v>-0.006196299208708235</v>
       </c>
     </row>
     <row r="259">
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>-0.08842520015341238</v>
+        <v>-0.08842547687882241</v>
       </c>
       <c r="D259" t="n">
-        <v>0.003968707300741477</v>
+        <v>0.009487758687732776</v>
       </c>
     </row>
     <row r="260">
@@ -4580,10 +4580,10 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>0.2162283940895156</v>
+        <v>0.2162283483528642</v>
       </c>
       <c r="D260" t="n">
-        <v>0.009352201352918338</v>
+        <v>0.002010582112603426</v>
       </c>
     </row>
     <row r="261">
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>-0.00271151598922037</v>
+        <v>-0.002711417571461539</v>
       </c>
       <c r="D261" t="n">
-        <v>0.002587819294210113</v>
+        <v>-0.005490867482294937</v>
       </c>
     </row>
     <row r="262">
@@ -4615,7 +4615,7 @@
         <v>0.05168929683033152</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.001550558208105414</v>
+        <v>0.009032492194439365</v>
       </c>
     </row>
     <row r="263">
@@ -4631,7 +4631,7 @@
         <v>-0.08340742322443273</v>
       </c>
       <c r="D263" t="n">
-        <v>-0.005757932082856213</v>
+        <v>-0.01052702962657996</v>
       </c>
     </row>
     <row r="264">
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>-0.02387155883030456</v>
+        <v>-0.02387165814027903</v>
       </c>
       <c r="D264" t="n">
-        <v>0.00805906004461932</v>
+        <v>-0.009715999049608079</v>
       </c>
     </row>
     <row r="265">
@@ -4660,10 +4660,10 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>-0.01743247822851424</v>
+        <v>-0.01743228019491072</v>
       </c>
       <c r="D265" t="n">
-        <v>0.005156840808397081</v>
+        <v>0.0007405053602750908</v>
       </c>
     </row>
     <row r="266">
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>0.05164340532024347</v>
+        <v>0.05164329636868836</v>
       </c>
       <c r="D266" t="n">
-        <v>0.008700381567837189</v>
+        <v>-0.0004915128666576141</v>
       </c>
     </row>
     <row r="267">
@@ -4695,7 +4695,7 @@
         <v>-0.05220751903104515</v>
       </c>
       <c r="D267" t="n">
-        <v>0.004750505121167971</v>
+        <v>-0.004146361381329292</v>
       </c>
     </row>
     <row r="268">
@@ -4711,7 +4711,7 @@
         <v>-0.01327200988451183</v>
       </c>
       <c r="D268" t="n">
-        <v>0.006122325937852491</v>
+        <v>-0.00803243195233596</v>
       </c>
     </row>
     <row r="269">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>-0.001990503129976062</v>
+        <v>-0.001990610981874696</v>
       </c>
       <c r="D269" t="n">
-        <v>0.01143715899971845</v>
+        <v>-0.005928991893457592</v>
       </c>
     </row>
     <row r="270">
@@ -4740,10 +4740,10 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>-0.08151401699146499</v>
+        <v>-0.08151379883767784</v>
       </c>
       <c r="D270" t="n">
-        <v>0.01182622297588413</v>
+        <v>-0.008880656367595441</v>
       </c>
     </row>
     <row r="271">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>-0.04760851950472278</v>
+        <v>-0.04760851649668718</v>
       </c>
       <c r="D271" t="n">
-        <v>0.007350296108906773</v>
+        <v>-0.0005880337400302462</v>
       </c>
     </row>
     <row r="272">
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>-0.0006798296083686539</v>
+        <v>-0.0006799331164160094</v>
       </c>
       <c r="D272" t="n">
-        <v>0.007035513977385664</v>
+        <v>-0.004539975875966223</v>
       </c>
     </row>
     <row r="273">
@@ -4791,7 +4791,7 @@
         <v>0.08624905555258289</v>
       </c>
       <c r="D273" t="n">
-        <v>0.01609491723562919</v>
+        <v>0.003697860333903087</v>
       </c>
     </row>
     <row r="274">
@@ -4807,7 +4807,7 @@
         <v>-0.02013142071914698</v>
       </c>
       <c r="D274" t="n">
-        <v>0.008138833038154773</v>
+        <v>-0.01095028018892285</v>
       </c>
     </row>
     <row r="275">
@@ -4823,7 +4823,7 @@
         <v>-0.03102902386608919</v>
       </c>
       <c r="D275" t="n">
-        <v>0.009199441783745922</v>
+        <v>-0.006722092633177029</v>
       </c>
     </row>
     <row r="276">
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>-0.03884866142691656</v>
+        <v>-0.03884860157941039</v>
       </c>
       <c r="D276" t="n">
-        <v>0.01196389827452319</v>
+        <v>-6.095688927664194e-05</v>
       </c>
     </row>
     <row r="277">
@@ -4852,10 +4852,10 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>0.03141882642327687</v>
+        <v>0.03141876337561311</v>
       </c>
       <c r="D277" t="n">
-        <v>0.005464851033244083</v>
+        <v>-0.009573754139294694</v>
       </c>
     </row>
     <row r="278">
@@ -4871,7 +4871,7 @@
         <v>0.248023712298475</v>
       </c>
       <c r="D278" t="n">
-        <v>0.005033894109999422</v>
+        <v>-0.009159627549774759</v>
       </c>
     </row>
     <row r="279">
@@ -4887,7 +4887,7 @@
         <v>-0.01034205687437706</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.005778297113081744</v>
+        <v>-0.01347770502705739</v>
       </c>
     </row>
     <row r="280">
@@ -4903,7 +4903,7 @@
         <v>-0.03826657580901804</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.006723205075894059</v>
+        <v>-0.01079129927632847</v>
       </c>
     </row>
     <row r="281">
@@ -4919,7 +4919,7 @@
         <v>0.05108143633491857</v>
       </c>
       <c r="D281" t="n">
-        <v>-0.001156449529711864</v>
+        <v>-0.005276617419797854</v>
       </c>
     </row>
     <row r="282">
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>-0.01159578564737984</v>
+        <v>-0.01159586609546293</v>
       </c>
       <c r="D282" t="n">
-        <v>0.003696184021272025</v>
+        <v>-0.003390719695164329</v>
       </c>
     </row>
     <row r="283">
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>0.01837580579264109</v>
+        <v>0.01837596942889874</v>
       </c>
       <c r="D283" t="n">
-        <v>0.003464559985358831</v>
+        <v>-0.0006595215042134155</v>
       </c>
     </row>
     <row r="284">
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>0.04567231441034258</v>
+        <v>0.04567239351156283</v>
       </c>
       <c r="D284" t="n">
-        <v>0.004246555134437162</v>
+        <v>0.005379174836583105</v>
       </c>
     </row>
     <row r="285">
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>0.03485271112909949</v>
+        <v>0.03485256140217574</v>
       </c>
       <c r="D285" t="n">
-        <v>0.002134921118417182</v>
+        <v>-0.008371911694494916</v>
       </c>
     </row>
     <row r="286">
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>-0.0561909668804631</v>
+        <v>-0.05619096852918415</v>
       </c>
       <c r="D286" t="n">
-        <v>0.001668194951391866</v>
+        <v>-0.007008955973594315</v>
       </c>
     </row>
     <row r="287">
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>0.0222874472206871</v>
+        <v>0.02228752142445833</v>
       </c>
       <c r="D287" t="n">
-        <v>0.004902091402404204</v>
+        <v>-0.004027775366723739</v>
       </c>
     </row>
     <row r="288">
@@ -5031,7 +5031,7 @@
         <v>0.01149015993317781</v>
       </c>
       <c r="D288" t="n">
-        <v>0.009249965625384639</v>
+        <v>-0.003245303887420574</v>
       </c>
     </row>
     <row r="289">
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>0.007230171218423287</v>
+        <v>0.007230247268434353</v>
       </c>
       <c r="D289" t="n">
-        <v>0.01079999672195658</v>
+        <v>-0.0009678191671864227</v>
       </c>
     </row>
     <row r="290">
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>0.01123641486066385</v>
+        <v>0.01123641683023724</v>
       </c>
       <c r="D290" t="n">
-        <v>0.006144948171747166</v>
+        <v>-0.004053506947312369</v>
       </c>
     </row>
     <row r="291">
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>-0.004261375378072474</v>
+        <v>-0.004261616599905871</v>
       </c>
       <c r="D291" t="n">
-        <v>0.009282996180456641</v>
+        <v>-0.007798477943690471</v>
       </c>
     </row>
     <row r="292">
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>-0.002143144003446951</v>
+        <v>-0.002142913468626384</v>
       </c>
       <c r="D292" t="n">
-        <v>0.005183993105400788</v>
+        <v>-0.004098188655572073</v>
       </c>
     </row>
     <row r="293">
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>0.07043896220793011</v>
+        <v>0.07043889018458416</v>
       </c>
       <c r="D293" t="n">
-        <v>-0.001110965895548273</v>
+        <v>-0.005284098675346741</v>
       </c>
     </row>
     <row r="294">
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>0.01814126679413119</v>
+        <v>0.01814120185148393</v>
       </c>
       <c r="D294" t="n">
-        <v>-0.003231611559010777</v>
+        <v>-0.005393739009671134</v>
       </c>
     </row>
     <row r="295">
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>0.004994341340885056</v>
+        <v>0.004994281957418245</v>
       </c>
       <c r="D295" t="n">
-        <v>-0.00597923000150304</v>
+        <v>-0.01123393721493968</v>
       </c>
     </row>
     <row r="296">
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>-0.00136880279362761</v>
+        <v>-0.001368563383719934</v>
       </c>
       <c r="D296" t="n">
-        <v>-0.002455461261187415</v>
+        <v>-0.01055437575072666</v>
       </c>
     </row>
     <row r="297">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>0.03918626949773585</v>
+        <v>0.03918626271414061</v>
       </c>
       <c r="D297" t="n">
-        <v>0.003043656076511138</v>
+        <v>-0.002825333833968394</v>
       </c>
     </row>
     <row r="298">
@@ -5188,10 +5188,10 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>0.03369985664230746</v>
+        <v>0.0336997435229982</v>
       </c>
       <c r="D298" t="n">
-        <v>0.004130561862500975</v>
+        <v>-0.005603267442324852</v>
       </c>
     </row>
     <row r="299">
@@ -5207,7 +5207,7 @@
         <v>0.03134329544689929</v>
       </c>
       <c r="D299" t="n">
-        <v>0.003348257591218014</v>
+        <v>-0.006435313270739871</v>
       </c>
     </row>
     <row r="300">
@@ -5223,7 +5223,7 @@
         <v>0.01022606769422396</v>
       </c>
       <c r="D300" t="n">
-        <v>-0.001949320611910471</v>
+        <v>-0.01179562119142239</v>
       </c>
     </row>
     <row r="301">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>0.011838151152469</v>
+        <v>0.01183804789996334</v>
       </c>
       <c r="D301" t="n">
-        <v>-0.0001915151637231789</v>
+        <v>-0.01192750407845318</v>
       </c>
     </row>
     <row r="302">
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>-0.003520500055725462</v>
+        <v>-0.003520301890278854</v>
       </c>
       <c r="D302" t="n">
-        <v>0.002835532600771997</v>
+        <v>-0.007084170861661148</v>
       </c>
     </row>
     <row r="303">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>0.00784491026628531</v>
+        <v>0.007844910620677936</v>
       </c>
       <c r="D303" t="n">
-        <v>0.004497605642649641</v>
+        <v>-0.008484767519452806</v>
       </c>
     </row>
     <row r="304">
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>-0.009663783472253606</v>
+        <v>-0.009663781175235253</v>
       </c>
       <c r="D304" t="n">
-        <v>0.01010330410611949</v>
+        <v>-0.005519203216244372</v>
       </c>
     </row>
     <row r="305">
@@ -5300,10 +5300,10 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>0.005151010296200464</v>
+        <v>0.00515089435301852</v>
       </c>
       <c r="D305" t="n">
-        <v>0.009063659104286638</v>
+        <v>-0.008850818001403891</v>
       </c>
     </row>
     <row r="306">
@@ -5319,7 +5319,7 @@
         <v>-0.009373039119808579</v>
       </c>
       <c r="D306" t="n">
-        <v>0.002899086474773038</v>
+        <v>-0.007995438319885447</v>
       </c>
     </row>
     <row r="307">
@@ -5335,7 +5335,7 @@
         <v>0.01772058684576705</v>
       </c>
       <c r="D307" t="n">
-        <v>0.001823148466874221</v>
+        <v>-0.006322814395347624</v>
       </c>
     </row>
     <row r="308">
@@ -5348,10 +5348,10 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>-0.01968352519933658</v>
+        <v>-0.01968363045983523</v>
       </c>
       <c r="D308" t="n">
-        <v>0.009723216637116169</v>
+        <v>0.003443150547778125</v>
       </c>
     </row>
     <row r="309">
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>-0.02309138797156196</v>
+        <v>-0.0230912776351595</v>
       </c>
       <c r="D309" t="n">
-        <v>0.01033074988939984</v>
+        <v>-0.008200972872194861</v>
       </c>
     </row>
     <row r="310">
@@ -5383,7 +5383,7 @@
         <v>-0.007664217585275024</v>
       </c>
       <c r="D310" t="n">
-        <v>0.01322306390811733</v>
+        <v>-0.005159775158764949</v>
       </c>
     </row>
     <row r="311">
@@ -5399,7 +5399,7 @@
         <v>-0.01773088671586565</v>
       </c>
       <c r="D311" t="n">
-        <v>0.0157667848675457</v>
+        <v>0.001566075024113644</v>
       </c>
     </row>
     <row r="312">
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>0.006383913825037002</v>
+        <v>0.006384022752028873</v>
       </c>
       <c r="D312" t="n">
-        <v>0.003618598718907781</v>
+        <v>-0.008607676592695243</v>
       </c>
     </row>
     <row r="313">
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>-0.004862466653226205</v>
+        <v>-0.004862574004905751</v>
       </c>
       <c r="D313" t="n">
-        <v>0.004169177283513561</v>
+        <v>-0.01150855570218357</v>
       </c>
     </row>
     <row r="314">
@@ -5444,10 +5444,10 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>0.02715735423360788</v>
+        <v>0.02715724884428239</v>
       </c>
       <c r="D314" t="n">
-        <v>0.00564014877325178</v>
+        <v>-0.006570255678803615</v>
       </c>
     </row>
     <row r="315">
@@ -5460,10 +5460,10 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>0.02230055067028269</v>
+        <v>0.02230065244877699</v>
       </c>
       <c r="D315" t="n">
-        <v>0.003966851352583149</v>
+        <v>-0.008443740640940455</v>
       </c>
     </row>
     <row r="316">
@@ -5479,7 +5479,7 @@
         <v>-0.006146684271945757</v>
       </c>
       <c r="D316" t="n">
-        <v>0.005727416764624978</v>
+        <v>-0.006969305001633227</v>
       </c>
     </row>
     <row r="317">
@@ -5492,10 +5492,10 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>-0.01097413219115251</v>
+        <v>-0.01097421008368427</v>
       </c>
       <c r="D317" t="n">
-        <v>-0.001197225982365892</v>
+        <v>-0.008666586668282848</v>
       </c>
     </row>
     <row r="318">
@@ -5511,7 +5511,7 @@
         <v>0.01988297858837362</v>
       </c>
       <c r="D318" t="n">
-        <v>-0.0001011185731582404</v>
+        <v>-0.002348359864896675</v>
       </c>
     </row>
     <row r="319">
@@ -5527,7 +5527,7 @@
         <v>-0.04950121432377563</v>
       </c>
       <c r="D319" t="n">
-        <v>0.001031491561691561</v>
+        <v>0.006498340995408913</v>
       </c>
     </row>
     <row r="320">
@@ -5543,7 +5543,7 @@
         <v>-0.06992387309106263</v>
       </c>
       <c r="D320" t="n">
-        <v>0.0062720401921909</v>
+        <v>-0.00466786201487402</v>
       </c>
     </row>
     <row r="321">
@@ -5559,7 +5559,7 @@
         <v>0.06901320282865275</v>
       </c>
       <c r="D321" t="n">
-        <v>0.01049171795575733</v>
+        <v>0.005296610481808094</v>
       </c>
     </row>
     <row r="322">
@@ -5575,7 +5575,7 @@
         <v>0.04266015384011035</v>
       </c>
       <c r="D322" t="n">
-        <v>0.00822557849234438</v>
+        <v>-0.00262287986950669</v>
       </c>
     </row>
     <row r="323">
@@ -5591,7 +5591,7 @@
         <v>-0.0005333596078430647</v>
       </c>
       <c r="D323" t="n">
-        <v>0.007435830460306616</v>
+        <v>-0.001889305683210159</v>
       </c>
     </row>
     <row r="324">
@@ -5607,7 +5607,7 @@
         <v>-0.01457685093810168</v>
       </c>
       <c r="D324" t="n">
-        <v>0.004861709801880756</v>
+        <v>-0.0002193247620894262</v>
       </c>
     </row>
     <row r="325">
@@ -5623,7 +5623,7 @@
         <v>-0.02254846331703764</v>
       </c>
       <c r="D325" t="n">
-        <v>0.006743334374380015</v>
+        <v>-0.008634501406720181</v>
       </c>
     </row>
     <row r="326">
@@ -5639,7 +5639,7 @@
         <v>0.01629736063567577</v>
       </c>
       <c r="D326" t="n">
-        <v>0.01228943325623475</v>
+        <v>-0.004260026070704449</v>
       </c>
     </row>
     <row r="327">
@@ -5655,7 +5655,7 @@
         <v>-0.02060432056156314</v>
       </c>
       <c r="D327" t="n">
-        <v>0.006741699975952514</v>
+        <v>0.001390129429401755</v>
       </c>
     </row>
     <row r="328">
@@ -5671,7 +5671,7 @@
         <v>0.02329442299060724</v>
       </c>
       <c r="D328" t="n">
-        <v>0.0002979720362695868</v>
+        <v>-0.003568887795496573</v>
       </c>
     </row>
     <row r="329">
@@ -5687,7 +5687,7 @@
         <v>0.02070566828243603</v>
       </c>
       <c r="D329" t="n">
-        <v>-0.001228652613296206</v>
+        <v>-0.002335335599778695</v>
       </c>
     </row>
     <row r="330">
@@ -5703,7 +5703,7 @@
         <v>-0.00607798597532061</v>
       </c>
       <c r="D330" t="n">
-        <v>-0.00317617494500396</v>
+        <v>-0.01128955393173886</v>
       </c>
     </row>
     <row r="331">
@@ -5719,7 +5719,7 @@
         <v>-0.05494023140921223</v>
       </c>
       <c r="D331" t="n">
-        <v>1.905763670760011e-05</v>
+        <v>-0.008397012952607748</v>
       </c>
     </row>
     <row r="332">
@@ -5735,7 +5735,7 @@
         <v>0.01636561653850888</v>
       </c>
       <c r="D332" t="n">
-        <v>0.005803938763265399</v>
+        <v>0.003974765343238871</v>
       </c>
     </row>
     <row r="333">
@@ -5751,7 +5751,7 @@
         <v>-0.06521898265701553</v>
       </c>
       <c r="D333" t="n">
-        <v>0.008019559996153527</v>
+        <v>-0.004189992626202796</v>
       </c>
     </row>
     <row r="334">
@@ -5767,7 +5767,7 @@
         <v>0.01649420003936175</v>
       </c>
       <c r="D334" t="n">
-        <v>0.01114324360590587</v>
+        <v>0.0006925699932593832</v>
       </c>
     </row>
     <row r="335">
@@ -5783,7 +5783,7 @@
         <v>0.001018168044757961</v>
       </c>
       <c r="D335" t="n">
-        <v>0.004123924142690583</v>
+        <v>-0.004781652464971888</v>
       </c>
     </row>
     <row r="336">
@@ -5799,7 +5799,7 @@
         <v>0.02765401508734122</v>
       </c>
       <c r="D336" t="n">
-        <v>0.005276455138254555</v>
+        <v>-0.008472136141480157</v>
       </c>
     </row>
     <row r="337">
@@ -5815,7 +5815,7 @@
         <v>-0.04689551454107876</v>
       </c>
       <c r="D337" t="n">
-        <v>0.00320196443241096</v>
+        <v>-0.006221086379533424</v>
       </c>
     </row>
     <row r="338">
@@ -5831,7 +5831,7 @@
         <v>-0.02369482221732311</v>
       </c>
       <c r="D338" t="n">
-        <v>0.006132407631486824</v>
+        <v>-0.007566650221710932</v>
       </c>
     </row>
     <row r="339">
@@ -5847,7 +5847,7 @@
         <v>-0.004632415776625765</v>
       </c>
       <c r="D339" t="n">
-        <v>0.01273106377127546</v>
+        <v>-0.003561129423164604</v>
       </c>
     </row>
     <row r="340">
@@ -5863,7 +5863,7 @@
         <v>0.08438110587212111</v>
       </c>
       <c r="D340" t="n">
-        <v>0.01217093822516847</v>
+        <v>-0.007527364798177416</v>
       </c>
     </row>
     <row r="341">
@@ -5879,7 +5879,7 @@
         <v>-0.008541360291376199</v>
       </c>
       <c r="D341" t="n">
-        <v>0.0005548790967444522</v>
+        <v>-0.008341478515132705</v>
       </c>
     </row>
     <row r="342">
@@ -5895,7 +5895,7 @@
         <v>-0.01290265580557626</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.001960414184601534</v>
+        <v>-0.007707769255905399</v>
       </c>
     </row>
     <row r="343">
@@ -5911,7 +5911,7 @@
         <v>0.004775631791148927</v>
       </c>
       <c r="D343" t="n">
-        <v>0.00752499269487761</v>
+        <v>0.004031639419536498</v>
       </c>
     </row>
     <row r="344">
@@ -5927,7 +5927,7 @@
         <v>0.02101305633917505</v>
       </c>
       <c r="D344" t="n">
-        <v>0.01056784884750311</v>
+        <v>-0.01112996773468052</v>
       </c>
     </row>
     <row r="345">
@@ -5943,7 +5943,7 @@
         <v>0.03683424813914216</v>
       </c>
       <c r="D345" t="n">
-        <v>0.01153609219184655</v>
+        <v>-0.003770281502909608</v>
       </c>
     </row>
     <row r="346">
@@ -5959,7 +5959,7 @@
         <v>0.06810212680122274</v>
       </c>
       <c r="D346" t="n">
-        <v>0.01073961812367063</v>
+        <v>-3.068455135356914e-05</v>
       </c>
     </row>
     <row r="347">
@@ -5975,7 +5975,7 @@
         <v>-0.01811146288480636</v>
       </c>
       <c r="D347" t="n">
-        <v>-0.004137481608370364</v>
+        <v>-0.01573331311412652</v>
       </c>
     </row>
     <row r="348">
@@ -5991,7 +5991,7 @@
         <v>0.08080965854733857</v>
       </c>
       <c r="D348" t="n">
-        <v>-0.0005366957731665987</v>
+        <v>-0.01370046265433604</v>
       </c>
     </row>
     <row r="349">
@@ -6007,7 +6007,7 @@
         <v>0.06282825024077821</v>
       </c>
       <c r="D349" t="n">
-        <v>-0.0008964607725745243</v>
+        <v>-0.009536607552728078</v>
       </c>
     </row>
     <row r="350">
@@ -6023,7 +6023,7 @@
         <v>-0.01926582351347317</v>
       </c>
       <c r="D350" t="n">
-        <v>-0.0003393608939347443</v>
+        <v>-0.01133271528628689</v>
       </c>
     </row>
     <row r="351">
@@ -6039,7 +6039,7 @@
         <v>0.02021773838352137</v>
       </c>
       <c r="D351" t="n">
-        <v>0.002180245574433842</v>
+        <v>-0.002433468894844599</v>
       </c>
     </row>
     <row r="352">
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>0.02601129971270577</v>
+        <v>0.02601146169037172</v>
       </c>
       <c r="D352" t="n">
-        <v>0.005696827872511827</v>
+        <v>-0.00065404088522564</v>
       </c>
     </row>
     <row r="353">
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>-0.1260849874540891</v>
+        <v>-0.1260850541840436</v>
       </c>
       <c r="D353" t="n">
-        <v>0.001648778911301966</v>
+        <v>-0.0006319852081739597</v>
       </c>
     </row>
     <row r="354">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>0.06168439516652913</v>
+        <v>0.06168430752245868</v>
       </c>
       <c r="D354" t="n">
-        <v>0.009951195848903754</v>
+        <v>0.01302752060924173</v>
       </c>
     </row>
     <row r="355">
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>-0.01049262542114371</v>
+        <v>-0.01049254659404086</v>
       </c>
       <c r="D355" t="n">
-        <v>0.0061740831369762</v>
+        <v>-0.001572455170987468</v>
       </c>
     </row>
     <row r="356">
@@ -6119,7 +6119,7 @@
         <v>0.01671168410434642</v>
       </c>
       <c r="D356" t="n">
-        <v>0.00939573511234704</v>
+        <v>0.0009532867885163696</v>
       </c>
     </row>
     <row r="357">
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>0.0960329235925339</v>
+        <v>0.09603300273851079</v>
       </c>
       <c r="D357" t="n">
-        <v>0.002964831450275146</v>
+        <v>-0.00197446829764385</v>
       </c>
     </row>
     <row r="358">
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>0.02626531035381496</v>
+        <v>0.02626516271828272</v>
       </c>
       <c r="D358" t="n">
-        <v>0.004745660738686927</v>
+        <v>-0.01082806967617369</v>
       </c>
     </row>
     <row r="359">
@@ -6164,10 +6164,10 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>0.04091469143012205</v>
+        <v>0.04091484180422567</v>
       </c>
       <c r="D359" t="n">
-        <v>0.00362250779859126</v>
+        <v>-0.00550176230138754</v>
       </c>
     </row>
     <row r="360">
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>-0.01162771021646625</v>
+        <v>-0.01162777888776489</v>
       </c>
       <c r="D360" t="n">
-        <v>0.0007112455417530358</v>
+        <v>-0.008212696551947236</v>
       </c>
     </row>
     <row r="361">
@@ -6199,7 +6199,7 @@
         <v>-0.05375318900336712</v>
       </c>
       <c r="D361" t="n">
-        <v>0.0081449215034981</v>
+        <v>-0.006346704307198688</v>
       </c>
     </row>
     <row r="362">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>0.01868584769287995</v>
+        <v>0.01868577343899602</v>
       </c>
       <c r="D362" t="n">
-        <v>0.006903470504756719</v>
+        <v>0.0001234102231456365</v>
       </c>
     </row>
     <row r="363">
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>0.08469703308191401</v>
+        <v>0.08469710559988319</v>
       </c>
       <c r="D363" t="n">
-        <v>0.001180116880638061</v>
+        <v>-0.003192864416984546</v>
       </c>
     </row>
     <row r="364">
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>-0.002688669920440034</v>
+        <v>-0.002688733573790847</v>
       </c>
       <c r="D364" t="n">
-        <v>-0.002591121893798905</v>
+        <v>-0.005602093055348388</v>
       </c>
     </row>
     <row r="365">
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>-0.009302492998377598</v>
+        <v>-0.009302491932401402</v>
       </c>
       <c r="D365" t="n">
-        <v>-0.006613155692503908</v>
+        <v>-0.008329739305177025</v>
       </c>
     </row>
     <row r="366">
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>-0.01272669435843565</v>
+        <v>-0.01272657367847385</v>
       </c>
       <c r="D366" t="n">
-        <v>-0.001527559991628542</v>
+        <v>-0.01124417500352809</v>
       </c>
     </row>
     <row r="367">
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>0.007837738675557038</v>
+        <v>0.007837676960469553</v>
       </c>
       <c r="D367" t="n">
-        <v>0.00511053983482501</v>
+        <v>-0.001523515362118017</v>
       </c>
     </row>
     <row r="368">
@@ -6311,7 +6311,7 @@
         <v>0.06258525590826847</v>
       </c>
       <c r="D368" t="n">
-        <v>0.006665142062965455</v>
+        <v>-0.001897220862141521</v>
       </c>
     </row>
     <row r="369">
@@ -6327,7 +6327,7 @@
         <v>0.03879227153260323</v>
       </c>
       <c r="D369" t="n">
-        <v>0.003962792506669302</v>
+        <v>-0.006989798973737806</v>
       </c>
     </row>
     <row r="370">
@@ -6343,7 +6343,7 @@
         <v>-0.03730024808829724</v>
       </c>
       <c r="D370" t="n">
-        <v>-0.002171010100420177</v>
+        <v>-0.01316539725361352</v>
       </c>
     </row>
     <row r="371">
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>-0.029146321259514</v>
+        <v>-0.02914643183840893</v>
       </c>
       <c r="D371" t="n">
-        <v>0.0003061208004297867</v>
+        <v>-0.008778730503666232</v>
       </c>
     </row>
     <row r="372">
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>0.001075980974635571</v>
+        <v>0.001075977495207603</v>
       </c>
       <c r="D372" t="n">
-        <v>0.006439847087072661</v>
+        <v>-0.003841218821770756</v>
       </c>
     </row>
     <row r="373">
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>0.0182124269057139</v>
+        <v>0.01821242771617915</v>
       </c>
       <c r="D373" t="n">
-        <v>0.008228752838244712</v>
+        <v>-0.007179210461163566</v>
       </c>
     </row>
     <row r="374">
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>0.01189421425605086</v>
+        <v>0.01189421421798786</v>
       </c>
       <c r="D374" t="n">
-        <v>0.01126027274047261</v>
+        <v>-0.003998799599322209</v>
       </c>
     </row>
     <row r="375">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>-0.03883181131419189</v>
+        <v>-0.03883169172539747</v>
       </c>
       <c r="D375" t="n">
-        <v>0.007439753177963705</v>
+        <v>-0.01039438148131134</v>
       </c>
     </row>
     <row r="376">
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>0.0794009870010568</v>
+        <v>0.07940087571783994</v>
       </c>
       <c r="D376" t="n">
-        <v>0.00343519991746496</v>
+        <v>-0.009905439114024861</v>
       </c>
     </row>
     <row r="377">
@@ -6452,10 +6452,10 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>0.03744247357093</v>
+        <v>0.03744256998981654</v>
       </c>
       <c r="D377" t="n">
-        <v>-0.0011269877879475</v>
+        <v>-0.01102262943574924</v>
       </c>
     </row>
     <row r="378">
@@ -6471,7 +6471,7 @@
         <v>0.0197637456811105</v>
       </c>
       <c r="D378" t="n">
-        <v>0.006854720815871186</v>
+        <v>0.0007293842146328102</v>
       </c>
     </row>
     <row r="379">
@@ -6487,7 +6487,7 @@
         <v>0.0237328111292463</v>
       </c>
       <c r="D379" t="n">
-        <v>0.003752636886706589</v>
+        <v>-0.009042097312376467</v>
       </c>
     </row>
     <row r="380">
@@ -6503,7 +6503,7 @@
         <v>0.03321531562850399</v>
       </c>
       <c r="D380" t="n">
-        <v>0.008510198736588518</v>
+        <v>-0.01147168677047143</v>
       </c>
     </row>
     <row r="381">
@@ -6519,7 +6519,7 @@
         <v>0.003448310458841863</v>
       </c>
       <c r="D381" t="n">
-        <v>0.01011317078168724</v>
+        <v>-0.002374626769014882</v>
       </c>
     </row>
     <row r="382">
@@ -6535,7 +6535,7 @@
         <v>0.003018405680200065</v>
       </c>
       <c r="D382" t="n">
-        <v>-0.001222747777792529</v>
+        <v>-0.010657509120116</v>
       </c>
     </row>
     <row r="383">
@@ -6551,7 +6551,7 @@
         <v>0.03702785596927516</v>
       </c>
       <c r="D383" t="n">
-        <v>0.001559454830029393</v>
+        <v>-0.01276659042354577</v>
       </c>
     </row>
     <row r="384">
@@ -6567,7 +6567,7 @@
         <v>-0.05275240248580448</v>
       </c>
       <c r="D384" t="n">
-        <v>0.002985482803040312</v>
+        <v>-0.008591678006309621</v>
       </c>
     </row>
     <row r="385">
@@ -6583,7 +6583,7 @@
         <v>0.02807601597634202</v>
       </c>
       <c r="D385" t="n">
-        <v>0.005806982271892499</v>
+        <v>-0.003666028859236021</v>
       </c>
     </row>
     <row r="386">
@@ -6599,7 +6599,7 @@
         <v>0.004445526371249731</v>
       </c>
       <c r="D386" t="n">
-        <v>0.007161105461994676</v>
+        <v>-0.004900102441554997</v>
       </c>
     </row>
     <row r="387">
@@ -6615,7 +6615,7 @@
         <v>0.007839452371939615</v>
       </c>
       <c r="D387" t="n">
-        <v>0.006655264775252585</v>
+        <v>0.001209106861634264</v>
       </c>
     </row>
     <row r="388">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>-0.1179887225479757</v>
+        <v>-0.1179886684894508</v>
       </c>
       <c r="D388" t="n">
-        <v>0.003474277302234422</v>
+        <v>0.002834510645234947</v>
       </c>
     </row>
     <row r="389">
@@ -6644,10 +6644,10 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>-0.01237686768751689</v>
+        <v>-0.0123768682204628</v>
       </c>
       <c r="D389" t="n">
-        <v>0.01111097361641339</v>
+        <v>0.01298044589538977</v>
       </c>
     </row>
     <row r="390">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>-0.03816357143528237</v>
+        <v>-0.03816362901360104</v>
       </c>
       <c r="D390" t="n">
-        <v>0.009915125218525873</v>
+        <v>0.001662586209782805</v>
       </c>
     </row>
     <row r="391">
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>0.02011967569861239</v>
+        <v>0.02011974001774242</v>
       </c>
       <c r="D391" t="n">
-        <v>0.01355914301652701</v>
+        <v>0.003034779123616317</v>
       </c>
     </row>
     <row r="392">
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>0.04833640110149484</v>
+        <v>0.04833633866543341</v>
       </c>
       <c r="D392" t="n">
-        <v>0.007336697702153392</v>
+        <v>-0.0002746962594738127</v>
       </c>
     </row>
     <row r="393">
@@ -6708,10 +6708,10 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>0.0181458770601256</v>
+        <v>0.0181458173769834</v>
       </c>
       <c r="D393" t="n">
-        <v>0.007945251005784599</v>
+        <v>-0.005180743005018126</v>
       </c>
     </row>
     <row r="394">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>0.08125175953770436</v>
+        <v>0.08125182399666542</v>
       </c>
       <c r="D394" t="n">
-        <v>0.005952763928020958</v>
+        <v>-0.004597773077884873</v>
       </c>
     </row>
     <row r="395">
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>0.01073495160989879</v>
+        <v>0.01073506466283214</v>
       </c>
       <c r="D395" t="n">
-        <v>0.001399495380180985</v>
+        <v>-0.01144214277998131</v>
       </c>
     </row>
     <row r="396">
@@ -6756,10 +6756,10 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>-0.02915894801248098</v>
+        <v>-0.02915906948914149</v>
       </c>
       <c r="D396" t="n">
-        <v>0.005718075264445019</v>
+        <v>-0.006716077763478528</v>
       </c>
     </row>
     <row r="397">
@@ -6772,10 +6772,10 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>0.02687897761328584</v>
+        <v>0.02687908857349108</v>
       </c>
       <c r="D397" t="n">
-        <v>0.003022050687139186</v>
+        <v>-0.00264464705170967</v>
       </c>
     </row>
     <row r="398">
@@ -6788,10 +6788,10 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>0.04565753429130248</v>
+        <v>0.04565743066555694</v>
       </c>
       <c r="D398" t="n">
-        <v>-0.001272061978249224</v>
+        <v>-0.007415371883178114</v>
       </c>
     </row>
     <row r="399">
@@ -6807,7 +6807,7 @@
         <v>0.05912983076795597</v>
       </c>
       <c r="D399" t="n">
-        <v>-0.00231312866246835</v>
+        <v>-0.003707488066564927</v>
       </c>
     </row>
     <row r="400">
@@ -6823,7 +6823,7 @@
         <v>-0.04829422737146272</v>
       </c>
       <c r="D400" t="n">
-        <v>-0.007990293711995555</v>
+        <v>-0.01020675017507585</v>
       </c>
     </row>
     <row r="401">
@@ -6839,7 +6839,7 @@
         <v>-0.1266424343322353</v>
       </c>
       <c r="D401" t="n">
-        <v>-0.0008066806403896195</v>
+        <v>-0.008328970662300724</v>
       </c>
     </row>
     <row r="402">
@@ -6855,7 +6855,7 @@
         <v>0.006917877440658193</v>
       </c>
       <c r="D402" t="n">
-        <v>0.009160699814704219</v>
+        <v>0.008850657055843031</v>
       </c>
     </row>
     <row r="403">
@@ -6871,7 +6871,7 @@
         <v>0.03672440514108621</v>
       </c>
       <c r="D403" t="n">
-        <v>0.01350488669243772</v>
+        <v>0.0008431704233467247</v>
       </c>
     </row>
     <row r="404">
@@ -6887,7 +6887,7 @@
         <v>0.05629690233609574</v>
       </c>
       <c r="D404" t="n">
-        <v>0.01021868843146222</v>
+        <v>9.90874558851329e-05</v>
       </c>
     </row>
     <row r="405">
@@ -6903,7 +6903,7 @@
         <v>-0.01613293710293195</v>
       </c>
       <c r="D405" t="n">
-        <v>-0.001758560477467024</v>
+        <v>-0.009321059568747941</v>
       </c>
     </row>
     <row r="406">
@@ -6919,7 +6919,7 @@
         <v>-0.02732207511252205</v>
       </c>
       <c r="D406" t="n">
-        <v>-0.0002635087175085222</v>
+        <v>-0.01350660753537285</v>
       </c>
     </row>
     <row r="407">
@@ -6935,7 +6935,7 @@
         <v>0.09482368141190134</v>
       </c>
       <c r="D407" t="n">
-        <v>0.004639233542667432</v>
+        <v>-0.00626255795714669</v>
       </c>
     </row>
     <row r="408">
@@ -6951,7 +6951,7 @@
         <v>0.03560155976060864</v>
       </c>
       <c r="D408" t="n">
-        <v>0.00303808430725468</v>
+        <v>-0.01146373402674466</v>
       </c>
     </row>
     <row r="409">
@@ -6967,7 +6967,7 @@
         <v>0.01839166156949745</v>
       </c>
       <c r="D409" t="n">
-        <v>0.006237596286309104</v>
+        <v>-0.007351574701600307</v>
       </c>
     </row>
     <row r="410">
@@ -6983,7 +6983,7 @@
         <v>-0.0001711277251470467</v>
       </c>
       <c r="D410" t="n">
-        <v>0.00220928854064137</v>
+        <v>-0.01091240832684083</v>
       </c>
     </row>
     <row r="411">
@@ -6999,7 +6999,7 @@
         <v>0.07784659329761645</v>
       </c>
       <c r="D411" t="n">
-        <v>0.0006541122144583644</v>
+        <v>-0.01430648597147986</v>
       </c>
     </row>
     <row r="412">
@@ -7015,7 +7015,7 @@
         <v>0.03130267043296686</v>
       </c>
       <c r="D412" t="n">
-        <v>-0.003065774715538589</v>
+        <v>-0.01166823565696253</v>
       </c>
     </row>
     <row r="413">
@@ -7031,7 +7031,7 @@
         <v>0.1407164042129069</v>
       </c>
       <c r="D413" t="n">
-        <v>0.00547783379754799</v>
+        <v>0.00294379297009336</v>
       </c>
     </row>
     <row r="414">
@@ -7047,7 +7047,7 @@
         <v>-0.01200887263877193</v>
       </c>
       <c r="D414" t="n">
-        <v>-0.001283262306108206</v>
+        <v>-0.01587352033417279</v>
       </c>
     </row>
     <row r="415">
@@ -7063,7 +7063,7 @@
         <v>-0.01147752467925123</v>
       </c>
       <c r="D415" t="n">
-        <v>0.004994395648481249</v>
+        <v>-0.0101473461601534</v>
       </c>
     </row>
     <row r="416">
@@ -7079,7 +7079,7 @@
         <v>-0.08809106069823103</v>
       </c>
       <c r="D416" t="n">
-        <v>0.008311581412062641</v>
+        <v>0.001745805490118585</v>
       </c>
     </row>
     <row r="417">
@@ -7095,7 +7095,7 @@
         <v>-0.001402639786836746</v>
       </c>
       <c r="D417" t="n">
-        <v>0.006423861466784288</v>
+        <v>-0.006204160084717974</v>
       </c>
     </row>
     <row r="418">
@@ -7111,7 +7111,7 @@
         <v>-0.007964405609070857</v>
       </c>
       <c r="D418" t="n">
-        <v>0.007813430139938035</v>
+        <v>-0.004057874431725943</v>
       </c>
     </row>
     <row r="419">
@@ -7127,7 +7127,7 @@
         <v>-0.0203671937837282</v>
       </c>
       <c r="D419" t="n">
-        <v>0.009252771514105695</v>
+        <v>-0.001230498215321963</v>
       </c>
     </row>
     <row r="420">
@@ -7143,7 +7143,7 @@
         <v>0.04223845662847969</v>
       </c>
       <c r="D420" t="n">
-        <v>0.006564115870763389</v>
+        <v>-0.00500549941618697</v>
       </c>
     </row>
     <row r="421">
@@ -7159,7 +7159,7 @@
         <v>-0.007793019788694622</v>
       </c>
       <c r="D421" t="n">
-        <v>0.007091947043911803</v>
+        <v>-0.008846943081397574</v>
       </c>
     </row>
     <row r="422">
@@ -7175,7 +7175,7 @@
         <v>0.06853587654786697</v>
       </c>
       <c r="D422" t="n">
-        <v>0.002141332082256777</v>
+        <v>-0.003492782631912288</v>
       </c>
     </row>
     <row r="423">
@@ -7191,7 +7191,7 @@
         <v>0.06112731923355397</v>
       </c>
       <c r="D423" t="n">
-        <v>-0.001267688929886687</v>
+        <v>-0.004023635973858323</v>
       </c>
     </row>
     <row r="424">
@@ -7207,7 +7207,7 @@
         <v>-0.1127256910159302</v>
       </c>
       <c r="D424" t="n">
-        <v>-0.005005956393444862</v>
+        <v>-0.0006903167942858141</v>
       </c>
     </row>
     <row r="425">
@@ -7223,7 +7223,7 @@
         <v>-0.05662752844051966</v>
       </c>
       <c r="D425" t="n">
-        <v>0.003714044655887552</v>
+        <v>-0.003040299932603512</v>
       </c>
     </row>
     <row r="426">
@@ -7239,7 +7239,7 @@
         <v>0.05780150395204409</v>
       </c>
       <c r="D426" t="n">
-        <v>0.01087783213593579</v>
+        <v>0.004460439197160126</v>
       </c>
     </row>
     <row r="427">
@@ -7255,7 +7255,7 @@
         <v>0.09482999679204807</v>
       </c>
       <c r="D427" t="n">
-        <v>0.0109440864128525</v>
+        <v>0.0003463924572513931</v>
       </c>
     </row>
     <row r="428">
@@ -7271,7 +7271,7 @@
         <v>-0.08450713546170152</v>
       </c>
       <c r="D428" t="n">
-        <v>0.005023470872304423</v>
+        <v>-0.001174326314132573</v>
       </c>
     </row>
     <row r="429">
@@ -7287,7 +7287,7 @@
         <v>0.03814228497784866</v>
       </c>
       <c r="D429" t="n">
-        <v>0.006774347340116803</v>
+        <v>0.00243542618913188</v>
       </c>
     </row>
     <row r="430">
@@ -7303,7 +7303,7 @@
         <v>0.02572087022834568</v>
       </c>
       <c r="D430" t="n">
-        <v>0.005813365413086559</v>
+        <v>-0.008362319415325432</v>
       </c>
     </row>
     <row r="431">
@@ -7319,7 +7319,7 @@
         <v>0.0189171560330148</v>
       </c>
       <c r="D431" t="n">
-        <v>0.01153289568257332</v>
+        <v>-0.005982170821223657</v>
       </c>
     </row>
     <row r="432">
@@ -7335,7 +7335,7 @@
         <v>-0.05291856786719729</v>
       </c>
       <c r="D432" t="n">
-        <v>0.00213488500086452</v>
+        <v>0.002106955985067564</v>
       </c>
     </row>
     <row r="433">
@@ -7351,7 +7351,7 @@
         <v>0.04018539150565725</v>
       </c>
       <c r="D433" t="n">
-        <v>-0.0005279373928956284</v>
+        <v>-0.005428712978611078</v>
       </c>
     </row>
     <row r="434">
@@ -7367,7 +7367,7 @@
         <v>0.05582317513308643</v>
       </c>
       <c r="D434" t="n">
-        <v>-0.0006593613592659562</v>
+        <v>-0.004052070704736989</v>
       </c>
     </row>
     <row r="435">
@@ -7383,7 +7383,7 @@
         <v>-0.02634040822525274</v>
       </c>
       <c r="D435" t="n">
-        <v>-0.004051854745970308</v>
+        <v>-0.01127101167633357</v>
       </c>
     </row>
     <row r="436">
@@ -7399,7 +7399,7 @@
         <v>0.03749022803927549</v>
       </c>
       <c r="D436" t="n">
-        <v>-0.001392491848202226</v>
+        <v>-0.005473616204026572</v>
       </c>
     </row>
     <row r="437">
@@ -7415,7 +7415,7 @@
         <v>-0.02170257938055375</v>
       </c>
       <c r="D437" t="n">
-        <v>0.001033618059501839</v>
+        <v>-0.002463149581131668</v>
       </c>
     </row>
     <row r="438">
@@ -7431,7 +7431,7 @@
         <v>-0.05865212144534437</v>
       </c>
       <c r="D438" t="n">
-        <v>0.006503352194886194</v>
+        <v>-0.005114616667273631</v>
       </c>
     </row>
     <row r="439">
@@ -7447,7 +7447,7 @@
         <v>-0.08060552026260215</v>
       </c>
       <c r="D439" t="n">
-        <v>0.00843410447825846</v>
+        <v>0.001090795379940874</v>
       </c>
     </row>
     <row r="440">
@@ -7463,7 +7463,7 @@
         <v>-0.01849996113408703</v>
       </c>
       <c r="D440" t="n">
-        <v>0.009842013011733364</v>
+        <v>-0.0009536751238851801</v>
       </c>
     </row>
     <row r="441">
@@ -7479,7 +7479,7 @@
         <v>0.02815570238226139</v>
       </c>
       <c r="D441" t="n">
-        <v>0.01016973794221861</v>
+        <v>-0.003134272652213827</v>
       </c>
     </row>
     <row r="442">
@@ -7495,7 +7495,7 @@
         <v>0.02852849497363441</v>
       </c>
       <c r="D442" t="n">
-        <v>0.00836492778805991</v>
+        <v>-0.002025681657481412</v>
       </c>
     </row>
     <row r="443">
@@ -7511,7 +7511,7 @@
         <v>0.05196856674364703</v>
       </c>
       <c r="D443" t="n">
-        <v>0.003624314019222725</v>
+        <v>-0.01106495225640359</v>
       </c>
     </row>
     <row r="444">
@@ -7527,7 +7527,7 @@
         <v>0.003155106659997409</v>
       </c>
       <c r="D444" t="n">
-        <v>0.005990840186405164</v>
+        <v>-0.01257206339053528</v>
       </c>
     </row>
     <row r="445">
@@ -7543,7 +7543,7 @@
         <v>0.007374075420132131</v>
       </c>
       <c r="D445" t="n">
-        <v>0.005106758877863543</v>
+        <v>-0.01214349130744587</v>
       </c>
     </row>
     <row r="446">
@@ -7559,7 +7559,7 @@
         <v>0.01085828111454967</v>
       </c>
       <c r="D446" t="n">
-        <v>0.0002683597994819504</v>
+        <v>-0.009896412503402533</v>
       </c>
     </row>
     <row r="447">
@@ -7575,7 +7575,7 @@
         <v>-0.04304852393908076</v>
       </c>
       <c r="D447" t="n">
-        <v>0.0002547653463588501</v>
+        <v>-0.007494886178070235</v>
       </c>
     </row>
     <row r="448">
@@ -7591,7 +7591,7 @@
         <v>-0.001218750785577649</v>
       </c>
       <c r="D448" t="n">
-        <v>0.01142683411495174</v>
+        <v>0.007378902466099465</v>
       </c>
     </row>
     <row r="449">
@@ -7607,7 +7607,7 @@
         <v>0.08664399594349814</v>
       </c>
       <c r="D449" t="n">
-        <v>0.01131219959732377</v>
+        <v>-0.006571206019366976</v>
       </c>
     </row>
     <row r="450">
@@ -7623,7 +7623,7 @@
         <v>0.03090378936733629</v>
       </c>
       <c r="D450" t="n">
-        <v>0.01022482472290204</v>
+        <v>-0.00839839389965308</v>
       </c>
     </row>
     <row r="451">
@@ -7639,7 +7639,7 @@
         <v>0.01872127443640648</v>
       </c>
       <c r="D451" t="n">
-        <v>0.008351642048250301</v>
+        <v>4.9147725295429e-06</v>
       </c>
     </row>
     <row r="452">
@@ -7655,7 +7655,7 @@
         <v>0.04352211187977173</v>
       </c>
       <c r="D452" t="n">
-        <v>-0.004596331286310603</v>
+        <v>-0.01301867032941002</v>
       </c>
     </row>
     <row r="453">
@@ -7671,7 +7671,7 @@
         <v>-0.05327258973081461</v>
       </c>
       <c r="D453" t="n">
-        <v>-0.0008178075049135852</v>
+        <v>-0.01811516295660081</v>
       </c>
     </row>
     <row r="454">
@@ -7687,7 +7687,7 @@
         <v>0.01144235420462092</v>
       </c>
       <c r="D454" t="n">
-        <v>0.004520540322753278</v>
+        <v>-0.001332595503828392</v>
       </c>
     </row>
     <row r="455">
@@ -7703,7 +7703,7 @@
         <v>0.0006824682387827075</v>
       </c>
       <c r="D455" t="n">
-        <v>0.005166792019768154</v>
+        <v>-0.003913342103085487</v>
       </c>
     </row>
     <row r="456">
@@ -7719,7 +7719,7 @@
         <v>-0.03900747874150845</v>
       </c>
       <c r="D456" t="n">
-        <v>0.009539883693046747</v>
+        <v>-0.003973047532048864</v>
       </c>
     </row>
     <row r="457">
@@ -7735,7 +7735,7 @@
         <v>0.05403507742612912</v>
       </c>
       <c r="D457" t="n">
-        <v>0.0001593499237257587</v>
+        <v>-0.004756847122972604</v>
       </c>
     </row>
     <row r="458">
@@ -7751,7 +7751,7 @@
         <v>-0.1569425507968353</v>
       </c>
       <c r="D458" t="n">
-        <v>-0.005146420994922696</v>
+        <v>-0.003381284824034663</v>
       </c>
     </row>
     <row r="459">
@@ -7767,7 +7767,7 @@
         <v>0.02507672536536898</v>
       </c>
       <c r="D459" t="n">
-        <v>0.006582379474448632</v>
+        <v>0.01250949836037354</v>
       </c>
     </row>
     <row r="460">
@@ -7783,7 +7783,7 @@
         <v>-0.05144712596487677</v>
       </c>
       <c r="D460" t="n">
-        <v>0.007927799288523206</v>
+        <v>0.0001052871888292985</v>
       </c>
     </row>
     <row r="461">
@@ -7799,7 +7799,7 @@
         <v>0.06162113371362654</v>
       </c>
       <c r="D461" t="n">
-        <v>0.01421648617336107</v>
+        <v>0.00752802399063792</v>
       </c>
     </row>
     <row r="462">
@@ -7815,7 +7815,7 @@
         <v>0.08657297354382099</v>
       </c>
       <c r="D462" t="n">
-        <v>0.004416694803718779</v>
+        <v>0.001379543100153592</v>
       </c>
     </row>
     <row r="463">
@@ -7831,7 +7831,7 @@
         <v>0.0356204937933331</v>
       </c>
       <c r="D463" t="n">
-        <v>0.00499043388493849</v>
+        <v>-0.00879960867777139</v>
       </c>
     </row>
     <row r="464">
@@ -7847,7 +7847,7 @@
         <v>0.05021555212069095</v>
       </c>
       <c r="D464" t="n">
-        <v>0.001630322282499338</v>
+        <v>-0.006857682796950296</v>
       </c>
     </row>
     <row r="465">
@@ -7863,7 +7863,7 @@
         <v>-0.05517572139038074</v>
       </c>
       <c r="D465" t="n">
-        <v>0.0003023524482900757</v>
+        <v>-0.01137742440962376</v>
       </c>
     </row>
     <row r="466">
@@ -7879,7 +7879,7 @@
         <v>-0.02294408839234796</v>
       </c>
       <c r="D466" t="n">
-        <v>0.009251712421127314</v>
+        <v>-0.001903008782768961</v>
       </c>
     </row>
     <row r="467">
@@ -7895,7 +7895,7 @@
         <v>-0.01730007177302362</v>
       </c>
       <c r="D467" t="n">
-        <v>0.00705633919393453</v>
+        <v>0.002019628393083931</v>
       </c>
     </row>
     <row r="468">
@@ -7911,7 +7911,7 @@
         <v>0.06406298495346119</v>
       </c>
       <c r="D468" t="n">
-        <v>0.003346606947250717</v>
+        <v>-0.001101635459690771</v>
       </c>
     </row>
     <row r="469">
@@ -7927,7 +7927,7 @@
         <v>0.02778326891063032</v>
       </c>
       <c r="D469" t="n">
-        <v>-0.001443473212479549</v>
+        <v>-0.004502072461531455</v>
       </c>
     </row>
     <row r="470">
@@ -7943,7 +7943,7 @@
         <v>-0.02798579516903277</v>
       </c>
       <c r="D470" t="n">
-        <v>-0.005450515524366257</v>
+        <v>-0.01116340441461688</v>
       </c>
     </row>
     <row r="471">
@@ -7959,7 +7959,7 @@
         <v>-0.01467026963829587</v>
       </c>
       <c r="D471" t="n">
-        <v>-0.001134259572329416</v>
+        <v>-0.009720681414373683</v>
       </c>
     </row>
     <row r="472">
@@ -7975,7 +7975,7 @@
         <v>0.008176982937453614</v>
       </c>
       <c r="D472" t="n">
-        <v>0.004672791202894278</v>
+        <v>0.0004589339237972001</v>
       </c>
     </row>
     <row r="473">
@@ -7991,7 +7991,7 @@
         <v>0.01330599638453256</v>
       </c>
       <c r="D473" t="n">
-        <v>0.007567206898332669</v>
+        <v>-0.003471734799781488</v>
       </c>
     </row>
     <row r="474">
@@ -8007,7 +8007,7 @@
         <v>0.02987114874878904</v>
       </c>
       <c r="D474" t="n">
-        <v>0.006225269223304764</v>
+        <v>-0.003849423723922114</v>
       </c>
     </row>
     <row r="475">
@@ -8023,7 +8023,7 @@
         <v>-0.03259534951258347</v>
       </c>
       <c r="D475" t="n">
-        <v>0.0004017147453046939</v>
+        <v>-0.01053332310669164</v>
       </c>
     </row>
     <row r="476">
@@ -8039,7 +8039,7 @@
         <v>-0.03042861161677712</v>
       </c>
       <c r="D476" t="n">
-        <v>0.002684732158235675</v>
+        <v>-0.009211122487375437</v>
       </c>
     </row>
     <row r="477">
@@ -8055,7 +8055,7 @@
         <v>0.03617409604555666</v>
       </c>
       <c r="D477" t="n">
-        <v>0.006684331822677571</v>
+        <v>-0.002550887649393824</v>
       </c>
     </row>
     <row r="478">
@@ -8071,7 +8071,7 @@
         <v>0.0001325496723539876</v>
       </c>
       <c r="D478" t="n">
-        <v>0.006515975916994651</v>
+        <v>-0.009972966705943508</v>
       </c>
     </row>
     <row r="479">
@@ -8087,7 +8087,7 @@
         <v>0.03327202707297805</v>
       </c>
       <c r="D479" t="n">
-        <v>0.01056059305180763</v>
+        <v>-0.00541433865507185</v>
       </c>
     </row>
     <row r="480">
@@ -8103,7 +8103,7 @@
         <v>0.03079807389697931</v>
       </c>
       <c r="D480" t="n">
-        <v>0.005732519673178995</v>
+        <v>-0.01110992428307885</v>
       </c>
     </row>
     <row r="481">
@@ -8119,7 +8119,7 @@
         <v>0.04928474375048708</v>
       </c>
       <c r="D481" t="n">
-        <v>0.0001925534220718634</v>
+        <v>-0.01295288413986908</v>
       </c>
     </row>
     <row r="482">
@@ -8135,7 +8135,7 @@
         <v>0.04881102526549108</v>
       </c>
       <c r="D482" t="n">
-        <v>-0.00383445196666578</v>
+        <v>-0.01086079522161393</v>
       </c>
     </row>
     <row r="483">
@@ -8151,7 +8151,7 @@
         <v>0.07671182142579569</v>
       </c>
       <c r="D483" t="n">
-        <v>0.004592306210089775</v>
+        <v>-0.0007034948397580754</v>
       </c>
     </row>
     <row r="484">
@@ -8167,7 +8167,7 @@
         <v>0.05623713779617323</v>
       </c>
       <c r="D484" t="n">
-        <v>0.002054103452384929</v>
+        <v>-0.01480540896030253</v>
       </c>
     </row>
     <row r="485">
@@ -8183,7 +8183,7 @@
         <v>-0.03366447732190458</v>
       </c>
       <c r="D485" t="n">
-        <v>0.004027318130369206</v>
+        <v>-0.01153291302483257</v>
       </c>
     </row>
     <row r="486">
@@ -8199,7 +8199,7 @@
         <v>0.007605122858587832</v>
       </c>
       <c r="D486" t="n">
-        <v>0.009109507266672007</v>
+        <v>0.001112445116484287</v>
       </c>
     </row>
     <row r="487">
@@ -8215,7 +8215,7 @@
         <v>0.001839346581064216</v>
       </c>
       <c r="D487" t="n">
-        <v>0.0001208877654576826</v>
+        <v>-0.00975297337239452</v>
       </c>
     </row>
     <row r="488">
@@ -8231,7 +8231,7 @@
         <v>0.04973221249297066</v>
       </c>
       <c r="D488" t="n">
-        <v>0.004400780988699412</v>
+        <v>-0.0095522945236018</v>
       </c>
     </row>
     <row r="489">
@@ -8247,7 +8247,7 @@
         <v>-0.01867789708167966</v>
       </c>
       <c r="D489" t="n">
-        <v>0.002288196940004858</v>
+        <v>-0.005748134693002369</v>
       </c>
     </row>
     <row r="490">
@@ -8263,7 +8263,7 @@
         <v>0.03161944348168477</v>
       </c>
       <c r="D490" t="n">
-        <v>0.003779442723587252</v>
+        <v>-0.007224411825334247</v>
       </c>
     </row>
     <row r="491">
@@ -8279,7 +8279,7 @@
         <v>0.03511503773832492</v>
       </c>
       <c r="D491" t="n">
-        <v>0.004923586313714081</v>
+        <v>-0.007625879587312858</v>
       </c>
     </row>
     <row r="492">
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>0.001430314479728745</v>
+        <v>0.001430313154685559</v>
       </c>
       <c r="D492" t="n">
-        <v>0.003037287273255252</v>
+        <v>-0.005954602628027467</v>
       </c>
     </row>
     <row r="493">
@@ -8308,10 +8308,10 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>0.02065139183441089</v>
+        <v>0.02065120685839905</v>
       </c>
       <c r="D493" t="n">
-        <v>0.001591265591046152</v>
+        <v>-0.0004005076790273955</v>
       </c>
     </row>
     <row r="494">
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="C494" t="n">
-        <v>0.03313258158724164</v>
+        <v>0.03313276619541528</v>
       </c>
       <c r="D494" t="n">
-        <v>0.002484349545134759</v>
+        <v>0.005701577163570875</v>
       </c>
     </row>
     <row r="495">
@@ -8340,10 +8340,10 @@
         </is>
       </c>
       <c r="C495" t="n">
-        <v>-0.03435975139901171</v>
+        <v>-0.03435983238171136</v>
       </c>
       <c r="D495" t="n">
-        <v>0.002012114235673051</v>
+        <v>-0.009412638698222895</v>
       </c>
     </row>
     <row r="496">
@@ -8359,7 +8359,7 @@
         <v>0.08007727469644355</v>
       </c>
       <c r="D496" t="n">
-        <v>0.005202025330998969</v>
+        <v>-0.001029362489157255</v>
       </c>
     </row>
     <row r="497">
@@ -8375,7 +8375,7 @@
         <v>0.06611650700649818</v>
       </c>
       <c r="D497" t="n">
-        <v>0.00247810197957491</v>
+        <v>-0.007155003691589211</v>
       </c>
     </row>
     <row r="498">
@@ -8391,7 +8391,7 @@
         <v>-0.01735586733834038</v>
       </c>
       <c r="D498" t="n">
-        <v>0.004319606674288621</v>
+        <v>-0.006180003187191066</v>
       </c>
     </row>
     <row r="499">
@@ -8407,7 +8407,7 @@
         <v>0.03327979900004185</v>
       </c>
       <c r="D499" t="n">
-        <v>0.004074793520890231</v>
+        <v>0.001367108112126893</v>
       </c>
     </row>
     <row r="500">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="C500" t="n">
-        <v>0.01614185775393961</v>
+        <v>0.01614193741055581</v>
       </c>
       <c r="D500" t="n">
-        <v>0.004320481038968227</v>
+        <v>-0.009022526363774137</v>
       </c>
     </row>
     <row r="501">
@@ -8436,10 +8436,10 @@
         </is>
       </c>
       <c r="C501" t="n">
-        <v>0.02570228254423168</v>
+        <v>0.02570227431332661</v>
       </c>
       <c r="D501" t="n">
-        <v>0.009189220140996499</v>
+        <v>-0.006254468952616632</v>
       </c>
     </row>
     <row r="502">
@@ -8452,10 +8452,10 @@
         </is>
       </c>
       <c r="C502" t="n">
-        <v>0.001620469983399708</v>
+        <v>0.001620390503191738</v>
       </c>
       <c r="D502" t="n">
-        <v>0.002475316229596477</v>
+        <v>-0.001235699898300923</v>
       </c>
     </row>
     <row r="503">
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="C503" t="n">
-        <v>-0.02775591947912359</v>
+        <v>-0.02775598814756697</v>
       </c>
       <c r="D503" t="n">
-        <v>-0.002828722382667213</v>
+        <v>-0.007203491613484523</v>
       </c>
     </row>
     <row r="504">
@@ -8484,10 +8484,10 @@
         </is>
       </c>
       <c r="C504" t="n">
-        <v>0.1000305874464522</v>
+        <v>0.1000308133082692</v>
       </c>
       <c r="D504" t="n">
-        <v>-0.0003651380152439425</v>
+        <v>0.001109908447450924</v>
       </c>
     </row>
     <row r="505">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="C505" t="n">
-        <v>0.05191251082250159</v>
+        <v>0.05191237484902111</v>
       </c>
       <c r="D505" t="n">
-        <v>-0.005421567641692508</v>
+        <v>-0.009776382637168811</v>
       </c>
     </row>
     <row r="506">
@@ -8516,10 +8516,10 @@
         </is>
       </c>
       <c r="C506" t="n">
-        <v>-0.03823682686160224</v>
+        <v>-0.03823688530066449</v>
       </c>
       <c r="D506" t="n">
-        <v>-0.003816613513008034</v>
+        <v>-0.01005478177011466</v>
       </c>
     </row>
     <row r="507">
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="C507" t="n">
-        <v>-0.0235991781441367</v>
+        <v>-0.02359911861899844</v>
       </c>
       <c r="D507" t="n">
-        <v>-0.001044320009682514</v>
+        <v>0.003715619351075576</v>
       </c>
     </row>
     <row r="508">
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="C508" t="n">
-        <v>-0.02534645719052497</v>
+        <v>-0.02534651730816073</v>
       </c>
       <c r="D508" t="n">
-        <v>0.006475372678049231</v>
+        <v>-0.005256908105943762</v>
       </c>
     </row>
     <row r="509">
@@ -8564,10 +8564,10 @@
         </is>
       </c>
       <c r="C509" t="n">
-        <v>-0.007405870585704744</v>
+        <v>-0.007405745008711495</v>
       </c>
       <c r="D509" t="n">
-        <v>0.01040464975818008</v>
+        <v>-0.002818077017203546</v>
       </c>
     </row>
     <row r="510">
@@ -8580,10 +8580,10 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>0.002562752123845713</v>
+        <v>0.002562628219984209</v>
       </c>
       <c r="D510" t="n">
-        <v>0.005190714235341069</v>
+        <v>-0.002392689326268803</v>
       </c>
     </row>
     <row r="511">
@@ -8596,10 +8596,10 @@
         </is>
       </c>
       <c r="C511" t="n">
-        <v>-0.02788215223465729</v>
+        <v>-0.02788202885714719</v>
       </c>
       <c r="D511" t="n">
-        <v>0.00449758139369094</v>
+        <v>-0.007516375813171194</v>
       </c>
     </row>
     <row r="512">
@@ -8612,10 +8612,10 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>0.06368658728445664</v>
+        <v>0.0636865852811318</v>
       </c>
       <c r="D512" t="n">
-        <v>0.006665321703791143</v>
+        <v>-0.005198344867109675</v>
       </c>
     </row>
     <row r="513">
@@ -8628,10 +8628,10 @@
         </is>
       </c>
       <c r="C513" t="n">
-        <v>-0.00719811208172505</v>
+        <v>-0.007198172221589361</v>
       </c>
       <c r="D513" t="n">
-        <v>0.003616179328560975</v>
+        <v>-0.01255806080062027</v>
       </c>
     </row>
     <row r="514">
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>0.001178615537464123</v>
+        <v>0.00117855311782944</v>
       </c>
       <c r="D514" t="n">
-        <v>0.00955000744212512</v>
+        <v>-0.007688826485619905</v>
       </c>
     </row>
     <row r="515">
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="C515" t="n">
-        <v>0.06636908904011163</v>
+        <v>0.06636916110982582</v>
       </c>
       <c r="D515" t="n">
-        <v>0.00626215362316333</v>
+        <v>-0.007709658860692289</v>
       </c>
     </row>
     <row r="516">
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="C516" t="n">
-        <v>0.06547103248370889</v>
+        <v>0.06547092193156168</v>
       </c>
       <c r="D516" t="n">
-        <v>0.0003638749473692119</v>
+        <v>-0.0121915675374371</v>
       </c>
     </row>
     <row r="517">
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="C517" t="n">
-        <v>-0.0348717430415737</v>
+        <v>-0.03487165339029552</v>
       </c>
       <c r="D517" t="n">
-        <v>-0.004708782926921388</v>
+        <v>-0.01081753049808011</v>
       </c>
     </row>
     <row r="518">
@@ -8711,7 +8711,7 @@
         <v>-0.01974840474770678</v>
       </c>
       <c r="D518" t="n">
-        <v>0.006011833000029308</v>
+        <v>0.005750542818299625</v>
       </c>
     </row>
     <row r="519">
@@ -8727,7 +8727,7 @@
         <v>-0.01289702278167404</v>
       </c>
       <c r="D519" t="n">
-        <v>0.009344238156727882</v>
+        <v>-0.007652350037268763</v>
       </c>
     </row>
     <row r="520">
@@ -8743,7 +8743,7 @@
         <v>-0.0008627648914477648</v>
       </c>
       <c r="D520" t="n">
-        <v>0.01511112242375139</v>
+        <v>-0.004433058631643522</v>
       </c>
     </row>
     <row r="521">
@@ -8759,7 +8759,7 @@
         <v>0.02482260502220623</v>
       </c>
       <c r="D521" t="n">
-        <v>0.01501397136978129</v>
+        <v>0.005310051857410601</v>
       </c>
     </row>
     <row r="522">
@@ -8775,7 +8775,7 @@
         <v>0.01680147263367116</v>
       </c>
       <c r="D522" t="n">
-        <v>0.0009708113855709634</v>
+        <v>-0.01093549226141346</v>
       </c>
     </row>
     <row r="523">
@@ -8791,7 +8791,7 @@
         <v>-0.08769432464280003</v>
       </c>
       <c r="D523" t="n">
-        <v>0.001511465918473413</v>
+        <v>-0.01370644331372665</v>
       </c>
     </row>
     <row r="524">
@@ -8807,7 +8807,7 @@
         <v>-0.06698738002076066</v>
       </c>
       <c r="D524" t="n">
-        <v>0.006967873111495119</v>
+        <v>-0.0006742540745214437</v>
       </c>
     </row>
     <row r="525">
@@ -8823,7 +8823,7 @@
         <v>0.07190838421147805</v>
       </c>
       <c r="D525" t="n">
-        <v>0.01137269537972333</v>
+        <v>4.498196395879075e-05</v>
       </c>
     </row>
     <row r="526">
@@ -8839,7 +8839,7 @@
         <v>0.01217338408037327</v>
       </c>
       <c r="D526" t="n">
-        <v>0.01139071308322043</v>
+        <v>-0.002244895643481907</v>
       </c>
     </row>
   </sheetData>
